--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\produits-cimentaires\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\produits-cimentaires\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B5D2CA-721E-4141-B75D-8721D5BFAD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088DC4CE-7F28-461E-8A06-B9FD07402509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="370">
   <si>
     <t>path</t>
   </si>
@@ -1143,6 +1143,9 @@
   </si>
   <si>
     <t>134</t>
+  </si>
+  <si>
+    <t>71121040</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1185,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1249,6 +1252,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1262,7 +1271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1290,12 +1299,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1351,6 +1354,45 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1693,7 +1735,7 @@
     <col min="2" max="2" width="52.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.77734375" style="5" customWidth="1"/>
   </cols>
@@ -1705,13 +1747,13 @@
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
@@ -1723,7 +1765,7 @@
       <c r="A2" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1732,7 +1774,7 @@
       <c r="D2" s="3">
         <v>28.48</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="5">
@@ -1743,7 +1785,7 @@
       <c r="A3" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1752,18 +1794,18 @@
       <c r="D3" s="3">
         <v>52.83</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="5">
-        <v>2.9999999993970405E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1772,50 +1814,50 @@
       <c r="D4" s="3">
         <v>74.100000000000009</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5">
-        <v>1.000000000040302E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="32">
         <v>30.5</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="5">
-        <v>47</v>
+      <c r="F5" s="33">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="32">
         <v>41.71</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="33">
         <v>9</v>
       </c>
     </row>
@@ -1823,19 +1865,19 @@
       <c r="A7" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="32">
         <v>74.62</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="33">
         <v>6</v>
       </c>
     </row>
@@ -1843,49 +1885,49 @@
       <c r="A8" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D8" s="3">
-        <v>7.15</v>
-      </c>
-      <c r="E8" s="15" t="s">
+      <c r="D8" s="34">
+        <v>7.76</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="5">
-        <v>112</v>
+      <c r="F8" s="35">
+        <v>1053</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="23" t="s">
+      <c r="A9" s="26"/>
+      <c r="B9" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="34">
         <v>8.69</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="23" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="34">
         <v>11.370000000000001</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="35">
         <v>0</v>
       </c>
     </row>
@@ -1893,34 +1935,34 @@
       <c r="A11" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D11" s="3">
-        <v>12.14</v>
-      </c>
-      <c r="E11" s="15" t="s">
+      <c r="D11" s="34">
+        <v>11.34</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="5">
-        <v>9</v>
+      <c r="F11" s="35">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="23" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="34">
         <v>1.8</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="35">
         <v>0</v>
       </c>
     </row>
@@ -1928,189 +1970,189 @@
       <c r="A13" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="34">
         <v>7.95</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="5">
-        <v>0</v>
+      <c r="F13" s="35">
+        <v>-5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="20" t="s">
         <v>50</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="34">
         <v>15.950000000000001</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="5">
-        <v>4</v>
+      <c r="F14" s="35">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="20" t="s">
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D15" s="3">
-        <v>11.76</v>
-      </c>
-      <c r="E15" s="15" t="s">
+      <c r="D15" s="34">
+        <v>12.4</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="5">
-        <v>0</v>
+      <c r="F15" s="35">
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="20" t="s">
         <v>52</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="34">
         <v>10.620000000000001</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="5">
-        <v>0</v>
+      <c r="F16" s="35">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="34">
         <v>45.34</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="23" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="34">
         <v>7.71</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="23" t="s">
+      <c r="A19" s="26"/>
+      <c r="B19" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="34">
         <v>25.18</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="23" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="34">
         <v>9.84</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="23" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="34">
         <v>11.43</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
-      <c r="B22" s="23" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="34">
         <v>13.55</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="22" t="s">
+      <c r="A23" s="26"/>
+      <c r="B23" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="34">
         <v>8.91</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2118,39 +2160,39 @@
       <c r="A24" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="20" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D24" s="3">
-        <v>11.53</v>
-      </c>
-      <c r="E24" s="15" t="s">
+      <c r="D24" s="34">
+        <v>12.870000000000001</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="5">
-        <v>0</v>
+      <c r="F24" s="35">
+        <v>-18</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="20" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="34">
         <v>9.24</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="35">
         <v>123</v>
       </c>
     </row>
@@ -2158,79 +2200,79 @@
       <c r="A26" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="20" t="s">
         <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D26" s="3">
-        <v>12.25</v>
-      </c>
-      <c r="E26" s="15" t="s">
+      <c r="D26" s="34">
+        <v>12.870000000000001</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="5">
-        <v>84</v>
+      <c r="F26" s="35">
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="23" t="s">
+      <c r="A27" s="26"/>
+      <c r="B27" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="34">
         <v>10.370000000000001</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
-      <c r="B28" s="23" t="s">
+      <c r="A28" s="26"/>
+      <c r="B28" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="34">
         <v>10.67</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="28"/>
-      <c r="B29" s="22" t="s">
+      <c r="A29" s="26"/>
+      <c r="B29" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="34">
         <v>8.91</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
-      <c r="B30" s="23" t="s">
+      <c r="A30" s="26"/>
+      <c r="B30" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="34">
         <v>19.52</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2238,34 +2280,34 @@
       <c r="A31" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="20" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D31" s="3">
-        <v>22.37</v>
-      </c>
-      <c r="E31" s="15" t="s">
+      <c r="D31" s="34">
+        <v>23.28</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="35">
         <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="23" t="s">
+      <c r="A32" s="26"/>
+      <c r="B32" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="34">
         <v>31.470000000000002</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="35">
         <v>4</v>
       </c>
     </row>
@@ -2273,139 +2315,139 @@
       <c r="A33" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="20" t="s">
         <v>69</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D33" s="3">
-        <v>20.23</v>
-      </c>
-      <c r="E33" s="15" t="s">
+      <c r="D33" s="34">
+        <v>21.05</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="5">
-        <v>95</v>
+      <c r="F33" s="35">
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="14" t="s">
         <v>175</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="36">
         <v>5.51</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="F34" s="5">
-        <v>23</v>
+      <c r="F34" s="37">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="14" t="s">
         <v>176</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D35" s="3">
-        <v>8.4499999999999993</v>
-      </c>
-      <c r="E35" s="20" t="s">
+      <c r="D35" s="36">
+        <v>9</v>
+      </c>
+      <c r="E35" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F35" s="5">
-        <v>-6</v>
+      <c r="F35" s="37">
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="14" t="s">
         <v>177</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="36">
         <v>10.74</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="F36" s="5">
-        <v>32</v>
+      <c r="F36" s="37">
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D37" s="3">
-        <v>12.91</v>
-      </c>
-      <c r="E37" s="20" t="s">
+      <c r="D37" s="36">
+        <v>8.57</v>
+      </c>
+      <c r="E37" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="5">
-        <v>43</v>
+      <c r="F37" s="37">
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="14" t="s">
         <v>179</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="36">
         <v>7.5</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="5">
-        <v>143</v>
+      <c r="F38" s="37">
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="14" t="s">
         <v>180</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="36">
         <v>6.98</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="37">
         <v>70</v>
       </c>
     </row>
@@ -2422,7 +2464,7 @@
       <c r="D40" s="3">
         <v>6.6400000000000006</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="18" t="s">
         <v>76</v>
       </c>
       <c r="F40" s="5">
@@ -2439,14 +2481,14 @@
       <c r="C41" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="38">
         <v>10.35</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F41" s="5">
-        <v>0</v>
+      <c r="F41" s="39">
+        <v>-4</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2459,13 +2501,13 @@
       <c r="C42" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="38">
         <v>46.52</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="39">
         <v>28</v>
       </c>
     </row>
@@ -2479,14 +2521,14 @@
       <c r="C43" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="38">
         <v>11</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="F43" s="5">
-        <v>12</v>
+      <c r="F43" s="39">
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2499,14 +2541,14 @@
       <c r="C44" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="38">
         <v>52.19</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="5">
-        <v>9</v>
+      <c r="F44" s="39">
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2519,50 +2561,50 @@
       <c r="C45" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="38">
         <v>87.74</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F45" s="5">
-        <v>7</v>
+      <c r="F45" s="39">
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="28"/>
+      <c r="A46" s="26"/>
       <c r="B46" s="10" t="s">
         <v>187</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="38">
         <v>15.13</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F46" s="5">
-        <v>12</v>
+      <c r="F46" s="39">
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="28"/>
+      <c r="A47" s="26"/>
       <c r="B47" s="10" t="s">
         <v>188</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="38">
         <v>43.63</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="F47" s="5">
-        <v>6</v>
+      <c r="F47" s="39">
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2575,14 +2617,14 @@
       <c r="C48" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D48" s="3">
-        <v>14.18</v>
-      </c>
-      <c r="E48" s="20" t="s">
+      <c r="D48" s="38">
+        <v>14.59</v>
+      </c>
+      <c r="E48" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F48" s="5">
-        <v>1</v>
+      <c r="F48" s="39">
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2595,181 +2637,181 @@
       <c r="C49" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="38">
         <v>36.869999999999997</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="39">
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="28"/>
-      <c r="B50" s="14" t="s">
+      <c r="A50" s="26"/>
+      <c r="B50" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C50" s="30"/>
-      <c r="D50" s="12">
+      <c r="C50" s="28"/>
+      <c r="D50" s="38">
         <v>24.14</v>
       </c>
-      <c r="E50" s="21" t="s">
+      <c r="E50" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="28"/>
-      <c r="B51" s="14" t="s">
+      <c r="A51" s="26"/>
+      <c r="B51" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C51" s="30"/>
-      <c r="D51" s="12">
+      <c r="C51" s="28"/>
+      <c r="D51" s="38">
         <v>12.46</v>
       </c>
-      <c r="E51" s="21" t="s">
+      <c r="E51" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="28"/>
-      <c r="B52" s="14" t="s">
+      <c r="A52" s="26"/>
+      <c r="B52" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="12">
+      <c r="C52" s="28"/>
+      <c r="D52" s="38">
         <v>60.84</v>
       </c>
-      <c r="E52" s="21" t="s">
+      <c r="E52" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="28"/>
+      <c r="A53" s="26"/>
       <c r="B53" s="10" t="s">
         <v>194</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="38">
         <v>28.75</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F53" s="5">
-        <v>7</v>
+      <c r="F53" s="39">
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="28"/>
+      <c r="A54" s="26"/>
       <c r="B54" s="10" t="s">
         <v>195</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="38">
         <v>58.82</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="F54" s="5">
-        <v>17</v>
+      <c r="F54" s="39">
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="28"/>
+      <c r="A55" s="26"/>
       <c r="B55" s="10" t="s">
         <v>196</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="38">
         <v>23.490000000000002</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F55" s="5">
-        <v>12</v>
+      <c r="F55" s="39">
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="28"/>
+      <c r="A56" s="26"/>
       <c r="B56" s="10" t="s">
         <v>197</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="38">
         <v>59.9</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="39">
         <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="28"/>
-      <c r="B57" s="14" t="s">
+      <c r="A57" s="26"/>
+      <c r="B57" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="C57" s="30"/>
-      <c r="D57" s="12">
+      <c r="C57" s="28"/>
+      <c r="D57" s="38">
         <v>8.36</v>
       </c>
-      <c r="E57" s="21" t="s">
+      <c r="E57" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F57" s="11">
+      <c r="F57" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="28"/>
-      <c r="B58" s="14" t="s">
+      <c r="A58" s="26"/>
+      <c r="B58" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="C58" s="30"/>
-      <c r="D58" s="12">
+      <c r="C58" s="28"/>
+      <c r="D58" s="38">
         <v>33.200000000000003</v>
       </c>
-      <c r="E58" s="21" t="s">
+      <c r="E58" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="28"/>
-      <c r="B59" s="14" t="s">
+      <c r="A59" s="26"/>
+      <c r="B59" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C59" s="30"/>
-      <c r="D59" s="12">
+      <c r="C59" s="28"/>
+      <c r="D59" s="38">
         <v>39.57</v>
       </c>
-      <c r="E59" s="21" t="s">
+      <c r="E59" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="F59" s="11">
+      <c r="F59" s="39">
         <v>0</v>
       </c>
     </row>
@@ -2783,14 +2825,14 @@
       <c r="C60" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="38">
         <v>18.5</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F60" s="5">
-        <v>5</v>
+      <c r="F60" s="39">
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2803,14 +2845,14 @@
       <c r="C61" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="38">
         <v>20.990000000000002</v>
       </c>
-      <c r="E61" s="20" t="s">
+      <c r="E61" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F61" s="5">
-        <v>19</v>
+      <c r="F61" s="39">
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2823,14 +2865,14 @@
       <c r="C62" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="38">
         <v>48.1</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F62" s="5">
-        <v>1</v>
+      <c r="F62" s="39">
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2843,14 +2885,14 @@
       <c r="C63" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="38">
         <v>51.81</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="F63" s="5">
-        <v>2</v>
+      <c r="F63" s="39">
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2863,14 +2905,14 @@
       <c r="C64" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="40">
         <v>65.8</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F64" s="5">
-        <v>3</v>
+      <c r="F64" s="41">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2883,28 +2925,28 @@
       <c r="C65" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="40">
         <v>129.94999999999999</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="41">
         <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="40">
         <v>255.92000000000002</v>
       </c>
-      <c r="E66" s="20" t="s">
+      <c r="E66" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F66" s="5">
+      <c r="F66" s="41">
         <v>0</v>
       </c>
     </row>
@@ -2918,13 +2960,13 @@
       <c r="C67" s="2">
         <v>100</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="40">
         <v>11.8</v>
       </c>
-      <c r="E67" s="20" t="s">
+      <c r="E67" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F67" s="5">
+      <c r="F67" s="41">
         <v>3</v>
       </c>
     </row>
@@ -2938,14 +2980,14 @@
       <c r="C68" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="40">
         <v>13.16</v>
       </c>
-      <c r="E68" s="20" t="s">
+      <c r="E68" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="F68" s="5">
-        <v>3</v>
+      <c r="F68" s="41">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2958,14 +3000,14 @@
       <c r="C69" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D69" s="3">
-        <v>12.780000000000001</v>
-      </c>
-      <c r="E69" s="20" t="s">
+      <c r="D69" s="40">
+        <v>13.36</v>
+      </c>
+      <c r="E69" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F69" s="5">
-        <v>2</v>
+      <c r="F69" s="41">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2978,14 +3020,14 @@
       <c r="C70" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D70" s="3">
-        <v>13.16</v>
-      </c>
-      <c r="E70" s="20" t="s">
+      <c r="D70" s="40">
+        <v>13.36</v>
+      </c>
+      <c r="E70" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F70" s="5">
-        <v>6</v>
+      <c r="F70" s="41">
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2998,14 +3040,14 @@
       <c r="C71" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71" s="40">
         <v>14.14</v>
       </c>
-      <c r="E71" s="20" t="s">
+      <c r="E71" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F71" s="5">
-        <v>4</v>
+      <c r="F71" s="41">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3018,14 +3060,14 @@
       <c r="C72" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="40">
         <v>12.780000000000001</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="E72" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F72" s="5">
-        <v>3</v>
+      <c r="F72" s="41">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -3038,13 +3080,13 @@
       <c r="C73" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="40">
         <v>13.200000000000001</v>
       </c>
-      <c r="E73" s="20" t="s">
+      <c r="E73" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F73" s="41">
         <v>3</v>
       </c>
     </row>
@@ -3058,31 +3100,31 @@
       <c r="C74" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="40">
         <v>14.35</v>
       </c>
-      <c r="E74" s="20" t="s">
+      <c r="E74" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="F74" s="5">
-        <v>11</v>
+      <c r="F74" s="41">
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="28"/>
-      <c r="B75" s="13" t="s">
+      <c r="A75" s="26"/>
+      <c r="B75" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C75" s="30" t="s">
+      <c r="C75" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="D75" s="12">
+      <c r="D75" s="40">
         <v>31.02</v>
       </c>
-      <c r="E75" s="21" t="s">
+      <c r="E75" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="F75" s="11">
+      <c r="F75" s="41">
         <v>0</v>
       </c>
     </row>
@@ -3096,14 +3138,14 @@
       <c r="C76" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D76" s="3">
-        <v>24.5</v>
-      </c>
-      <c r="E76" s="20" t="s">
+      <c r="D76" s="40">
+        <v>24.88</v>
+      </c>
+      <c r="E76" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F76" s="5">
-        <v>5</v>
+      <c r="F76" s="41">
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3116,14 +3158,14 @@
       <c r="C77" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D77" s="3">
-        <v>28.22</v>
-      </c>
-      <c r="E77" s="20" t="s">
+      <c r="D77" s="40">
+        <v>28.64</v>
+      </c>
+      <c r="E77" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F77" s="5">
-        <v>7</v>
+      <c r="F77" s="41">
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3136,14 +3178,14 @@
       <c r="C78" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="40">
         <v>28.22</v>
       </c>
-      <c r="E78" s="20" t="s">
+      <c r="E78" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="F78" s="5">
-        <v>8</v>
+      <c r="F78" s="41">
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3156,14 +3198,14 @@
       <c r="C79" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79" s="40">
         <v>28.650000000000002</v>
       </c>
-      <c r="E79" s="20" t="s">
+      <c r="E79" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F79" s="5">
-        <v>7</v>
+      <c r="F79" s="41">
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -3176,14 +3218,14 @@
       <c r="C80" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D80" s="3">
-        <v>20.3</v>
-      </c>
-      <c r="E80" s="20" t="s">
+      <c r="D80" s="40">
+        <v>20.61</v>
+      </c>
+      <c r="E80" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="F80" s="5">
-        <v>9</v>
+      <c r="F80" s="41">
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3196,13 +3238,13 @@
       <c r="C81" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="40">
         <v>28.25</v>
       </c>
-      <c r="E81" s="20" t="s">
+      <c r="E81" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="41">
         <v>8</v>
       </c>
     </row>
@@ -3216,14 +3258,14 @@
       <c r="C82" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="40">
         <v>25.92</v>
       </c>
-      <c r="E82" s="20" t="s">
+      <c r="E82" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="F82" s="5">
-        <v>6</v>
+      <c r="F82" s="41">
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3236,14 +3278,14 @@
       <c r="C83" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D83" s="3">
-        <v>27.45</v>
-      </c>
-      <c r="E83" s="20" t="s">
+      <c r="D83" s="40">
+        <v>27.87</v>
+      </c>
+      <c r="E83" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="F83" s="5">
-        <v>2</v>
+      <c r="F83" s="41">
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3256,14 +3298,14 @@
       <c r="C84" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D84" s="3">
-        <v>27.41</v>
-      </c>
-      <c r="E84" s="20" t="s">
+      <c r="D84" s="40">
+        <v>28.64</v>
+      </c>
+      <c r="E84" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="F84" s="5">
-        <v>3</v>
+      <c r="F84" s="41">
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -3276,13 +3318,13 @@
       <c r="C85" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D85" s="40">
         <v>19.7</v>
       </c>
-      <c r="E85" s="20" t="s">
+      <c r="E85" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="41">
         <v>0</v>
       </c>
     </row>
@@ -3290,17 +3332,17 @@
       <c r="A86" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C86" s="30"/>
-      <c r="D86" s="12">
+      <c r="C86" s="28"/>
+      <c r="D86" s="40">
         <v>79.86</v>
       </c>
-      <c r="E86" s="21" t="s">
+      <c r="E86" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F86" s="11">
+      <c r="F86" s="41">
         <v>5</v>
       </c>
     </row>
@@ -3314,13 +3356,13 @@
       <c r="C87" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D87" s="3">
+      <c r="D87" s="40">
         <v>111.09</v>
       </c>
-      <c r="E87" s="20" t="s">
+      <c r="E87" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F87" s="5">
+      <c r="F87" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3334,14 +3376,14 @@
       <c r="C88" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D88" s="3">
-        <v>76.460000000000008</v>
-      </c>
-      <c r="E88" s="20" t="s">
+      <c r="D88" s="40">
+        <v>79.92</v>
+      </c>
+      <c r="E88" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F88" s="5">
-        <v>0</v>
+      <c r="F88" s="41">
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -3354,14 +3396,14 @@
       <c r="C89" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D89" s="3">
-        <v>20.400000000000002</v>
-      </c>
-      <c r="E89" s="20" t="s">
+      <c r="D89" s="40">
+        <v>20.7</v>
+      </c>
+      <c r="E89" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="F89" s="5">
-        <v>4</v>
+      <c r="F89" s="41">
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -3374,14 +3416,14 @@
       <c r="C90" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90" s="40">
         <v>56</v>
       </c>
-      <c r="E90" s="20" t="s">
+      <c r="E90" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F90" s="5">
-        <v>3</v>
+      <c r="F90" s="41">
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -3394,14 +3436,14 @@
       <c r="C91" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="40">
         <v>112</v>
       </c>
-      <c r="E91" s="20" t="s">
+      <c r="E91" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="F91" s="5">
-        <v>3</v>
+      <c r="F91" s="41">
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3414,13 +3456,13 @@
       <c r="C92" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="40">
         <v>64.17</v>
       </c>
-      <c r="E92" s="20" t="s">
+      <c r="E92" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92" s="41">
         <v>2</v>
       </c>
     </row>
@@ -3434,14 +3476,14 @@
       <c r="C93" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D93" s="3">
-        <v>12.48</v>
-      </c>
-      <c r="E93" s="20" t="s">
+      <c r="D93" s="40">
+        <v>12.68</v>
+      </c>
+      <c r="E93" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F93" s="5">
-        <v>1</v>
+      <c r="F93" s="41">
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3454,14 +3496,14 @@
       <c r="C94" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D94" s="3">
-        <v>12.700000000000001</v>
-      </c>
-      <c r="E94" s="20" t="s">
+      <c r="D94" s="40">
+        <v>12.91</v>
+      </c>
+      <c r="E94" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="F94" s="5">
-        <v>6</v>
+      <c r="F94" s="41">
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3474,13 +3516,13 @@
       <c r="C95" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D95" s="3">
+      <c r="D95" s="40">
         <v>27.330000000000002</v>
       </c>
-      <c r="E95" s="20" t="s">
+      <c r="E95" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F95" s="5">
+      <c r="F95" s="41">
         <v>0</v>
       </c>
     </row>
@@ -3494,13 +3536,13 @@
       <c r="C96" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="40">
         <v>33.5</v>
       </c>
-      <c r="E96" s="20" t="s">
+      <c r="E96" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F96" s="5">
+      <c r="F96" s="41">
         <v>5</v>
       </c>
     </row>
@@ -3514,14 +3556,14 @@
       <c r="C97" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D97" s="3">
-        <v>38.32</v>
-      </c>
-      <c r="E97" s="20" t="s">
+      <c r="D97" s="40">
+        <v>38.880000000000003</v>
+      </c>
+      <c r="E97" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="F97" s="5">
-        <v>2</v>
+      <c r="F97" s="41">
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3534,13 +3576,13 @@
       <c r="C98" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98" s="40">
         <v>8.66</v>
       </c>
-      <c r="E98" s="20" t="s">
+      <c r="E98" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F98" s="5">
+      <c r="F98" s="41">
         <v>4</v>
       </c>
     </row>
@@ -3554,28 +3596,28 @@
       <c r="C99" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="40">
         <v>69.650000000000006</v>
       </c>
-      <c r="E99" s="20" t="s">
+      <c r="E99" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="F99" s="5">
+      <c r="F99" s="41">
         <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="28"/>
-      <c r="B100" s="13" t="s">
+      <c r="A100" s="26"/>
+      <c r="B100" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="40">
         <v>24.650000000000002</v>
       </c>
-      <c r="E100" s="20" t="s">
+      <c r="E100" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="F100" s="5">
+      <c r="F100" s="41">
         <v>0</v>
       </c>
     </row>
@@ -3589,28 +3631,28 @@
       <c r="C101" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D101" s="3">
-        <v>46.5</v>
-      </c>
-      <c r="E101" s="20" t="s">
+      <c r="D101" s="40">
+        <v>47.19</v>
+      </c>
+      <c r="E101" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="F101" s="5">
-        <v>1</v>
+      <c r="F101" s="41">
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="28"/>
-      <c r="B102" s="13" t="s">
+      <c r="A102" s="26"/>
+      <c r="B102" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="40">
         <v>29.080000000000002</v>
       </c>
-      <c r="E102" s="20" t="s">
+      <c r="E102" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="F102" s="5">
+      <c r="F102" s="41">
         <v>0</v>
       </c>
     </row>
@@ -3624,188 +3666,188 @@
       <c r="C103" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D103" s="3">
+      <c r="D103" s="40">
         <v>32.69</v>
       </c>
-      <c r="E103" s="20" t="s">
+      <c r="E103" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="F103" s="5">
-        <v>78</v>
+      <c r="F103" s="41">
+        <v>105</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="28"/>
+      <c r="A104" s="26"/>
       <c r="B104" s="9" t="s">
         <v>243</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D104" s="40">
         <v>24.26</v>
       </c>
-      <c r="E104" s="20" t="s">
+      <c r="E104" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="41">
         <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="28"/>
+      <c r="A105" s="26"/>
       <c r="B105" s="9" t="s">
         <v>244</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D105" s="3">
+      <c r="D105" s="40">
         <v>23.1</v>
       </c>
-      <c r="E105" s="20" t="s">
+      <c r="E105" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="F105" s="5">
+      <c r="F105" s="41">
         <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="28"/>
+      <c r="A106" s="26"/>
       <c r="B106" s="9" t="s">
         <v>245</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D106" s="3">
+      <c r="D106" s="40">
         <v>7.8</v>
       </c>
-      <c r="E106" s="20" t="s">
+      <c r="E106" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F106" s="5">
-        <v>6</v>
+      <c r="F106" s="41">
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="28"/>
-      <c r="B107" s="13" t="s">
+      <c r="A107" s="26"/>
+      <c r="B107" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="D107" s="3">
+      <c r="D107" s="40">
         <v>7.51</v>
       </c>
-      <c r="E107" s="20" t="s">
+      <c r="E107" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="F107" s="5">
-        <v>0</v>
+      <c r="F107" s="41">
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="28"/>
+      <c r="A108" s="26"/>
       <c r="B108" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D108" s="40">
         <v>17.16</v>
       </c>
-      <c r="E108" s="20" t="s">
+      <c r="E108" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="F108" s="5">
-        <v>10</v>
+      <c r="F108" s="41">
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="28"/>
+      <c r="A109" s="26"/>
       <c r="B109" s="9" t="s">
         <v>248</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D109" s="40">
         <v>16.5</v>
       </c>
-      <c r="E109" s="20" t="s">
+      <c r="E109" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="F109" s="5">
-        <v>2</v>
+      <c r="F109" s="41">
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="28"/>
+      <c r="A110" s="26"/>
       <c r="B110" s="9" t="s">
         <v>249</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D110" s="40">
         <v>8.4499999999999993</v>
       </c>
-      <c r="E110" s="20" t="s">
+      <c r="E110" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F110" s="5">
-        <v>19</v>
+      <c r="F110" s="41">
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="28"/>
+      <c r="A111" s="26"/>
       <c r="B111" s="9" t="s">
         <v>250</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D111" s="3">
-        <v>30.060000000000002</v>
-      </c>
-      <c r="E111" s="20" t="s">
+      <c r="D111" s="40">
+        <v>30.66</v>
+      </c>
+      <c r="E111" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="F111" s="5">
-        <v>0</v>
+      <c r="F111" s="41">
+        <v>30</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="28"/>
+      <c r="A112" s="26"/>
       <c r="B112" s="9" t="s">
         <v>251</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D112" s="3">
+      <c r="D112" s="40">
         <v>32.44</v>
       </c>
-      <c r="E112" s="20" t="s">
+      <c r="E112" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F112" s="5">
+      <c r="F112" s="41">
         <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="28"/>
+      <c r="A113" s="26"/>
       <c r="B113" s="9" t="s">
         <v>252</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D113" s="3">
+      <c r="D113" s="40">
         <v>8.86</v>
       </c>
-      <c r="E113" s="20" t="s">
+      <c r="E113" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="F113" s="5">
-        <v>0</v>
+      <c r="F113" s="41">
+        <v>-1</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3818,14 +3860,14 @@
       <c r="C114" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D114" s="40">
         <v>19.02</v>
       </c>
-      <c r="E114" s="20" t="s">
+      <c r="E114" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F114" s="5">
-        <v>0</v>
+      <c r="F114" s="41">
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -3838,32 +3880,32 @@
       <c r="C115" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D115" s="3">
+      <c r="D115" s="40">
         <v>51.44</v>
       </c>
-      <c r="E115" s="20" t="s">
+      <c r="E115" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="F115" s="5">
+      <c r="F115" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="28"/>
+      <c r="A116" s="26"/>
       <c r="B116" s="9" t="s">
         <v>255</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D116" s="3">
+      <c r="D116" s="40">
         <v>11.58</v>
       </c>
-      <c r="E116" s="20" t="s">
+      <c r="E116" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="F116" s="5">
-        <v>0</v>
+      <c r="F116" s="41">
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -3876,13 +3918,13 @@
       <c r="C117" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D117" s="40">
         <v>35.56</v>
       </c>
-      <c r="E117" s="20" t="s">
+      <c r="E117" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="F117" s="5">
+      <c r="F117" s="41">
         <v>5</v>
       </c>
     </row>
@@ -3896,310 +3938,310 @@
       <c r="C118" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D118" s="3">
+      <c r="D118" s="40">
         <v>89.14</v>
       </c>
-      <c r="E118" s="20" t="s">
+      <c r="E118" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="F118" s="5">
+      <c r="F118" s="41">
         <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="28"/>
+      <c r="A119" s="26"/>
       <c r="B119" s="9" t="s">
         <v>258</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D119" s="3">
+      <c r="D119" s="40">
         <v>24.32</v>
       </c>
-      <c r="E119" s="20" t="s">
+      <c r="E119" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="F119" s="5">
+      <c r="F119" s="41">
         <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="28"/>
+      <c r="A120" s="26"/>
       <c r="B120" s="9" t="s">
         <v>259</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D120" s="3">
+      <c r="D120" s="40">
         <v>31.240000000000002</v>
       </c>
-      <c r="E120" s="20" t="s">
+      <c r="E120" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="F120" s="5">
+      <c r="F120" s="41">
         <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="28"/>
+      <c r="A121" s="26"/>
       <c r="B121" s="9" t="s">
         <v>260</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D121" s="3">
+      <c r="D121" s="40">
         <v>28.82</v>
       </c>
-      <c r="E121" s="20" t="s">
+      <c r="E121" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="F121" s="5">
+      <c r="F121" s="41">
         <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="28"/>
+      <c r="A122" s="26"/>
       <c r="B122" s="9" t="s">
         <v>261</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D122" s="3">
+      <c r="D122" s="40">
         <v>72.710000000000008</v>
       </c>
-      <c r="E122" s="20" t="s">
+      <c r="E122" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="F122" s="5">
+      <c r="F122" s="41">
         <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="28"/>
+      <c r="A123" s="26"/>
       <c r="B123" s="9" t="s">
         <v>262</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D123" s="3">
+      <c r="D123" s="40">
         <v>9.64</v>
       </c>
-      <c r="E123" s="20" t="s">
+      <c r="E123" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="F123" s="5">
-        <v>4</v>
+      <c r="F123" s="41">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="28"/>
+      <c r="A124" s="26"/>
       <c r="B124" s="9" t="s">
         <v>263</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D124" s="40">
         <v>23.8</v>
       </c>
-      <c r="E124" s="20" t="s">
+      <c r="E124" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="F124" s="5">
+      <c r="F124" s="41">
         <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="28"/>
+      <c r="A125" s="26"/>
       <c r="B125" s="9" t="s">
         <v>264</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D125" s="3">
+      <c r="D125" s="40">
         <v>35.68</v>
       </c>
-      <c r="E125" s="20" t="s">
+      <c r="E125" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="F125" s="5">
+      <c r="F125" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="28"/>
+      <c r="A126" s="26"/>
       <c r="B126" s="9" t="s">
         <v>265</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D126" s="3">
+      <c r="D126" s="40">
         <v>18.22</v>
       </c>
-      <c r="E126" s="20" t="s">
+      <c r="E126" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="F126" s="5">
-        <v>25</v>
+      <c r="F126" s="41">
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="28"/>
+      <c r="A127" s="26"/>
       <c r="B127" s="9" t="s">
         <v>266</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D127" s="3">
+      <c r="D127" s="40">
         <v>18.150000000000002</v>
       </c>
-      <c r="E127" s="20" t="s">
+      <c r="E127" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F127" s="5">
+      <c r="F127" s="41">
         <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="28"/>
+      <c r="A128" s="26"/>
       <c r="B128" s="9" t="s">
         <v>267</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D128" s="3">
+      <c r="D128" s="40">
         <v>15.32</v>
       </c>
-      <c r="E128" s="20" t="s">
+      <c r="E128" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F128" s="5">
-        <v>19</v>
+      <c r="F128" s="41">
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="28"/>
+      <c r="A129" s="26"/>
       <c r="B129" s="9" t="s">
         <v>268</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D129" s="3">
+      <c r="D129" s="40">
         <v>29.5</v>
       </c>
-      <c r="E129" s="20" t="s">
+      <c r="E129" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="F129" s="5">
+      <c r="F129" s="41">
         <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="28"/>
+      <c r="A130" s="26"/>
       <c r="B130" s="9" t="s">
         <v>269</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D130" s="3">
+      <c r="D130" s="40">
         <v>44</v>
       </c>
-      <c r="E130" s="20" t="s">
+      <c r="E130" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="F130" s="5">
-        <v>17</v>
+      <c r="F130" s="41">
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="28"/>
+      <c r="A131" s="26"/>
       <c r="B131" s="9" t="s">
         <v>270</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D131" s="3">
+      <c r="D131" s="40">
         <v>64</v>
       </c>
-      <c r="E131" s="20" t="s">
+      <c r="E131" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F131" s="5">
+      <c r="F131" s="41">
         <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="28"/>
-      <c r="B132" s="13" t="s">
+      <c r="A132" s="26"/>
+      <c r="B132" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="D132" s="3">
+      <c r="D132" s="40">
         <v>18.37</v>
       </c>
-      <c r="E132" s="20" t="s">
+      <c r="E132" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="F132" s="5">
+      <c r="F132" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="28"/>
-      <c r="B133" s="13" t="s">
+      <c r="A133" s="26"/>
+      <c r="B133" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D133" s="3">
+      <c r="D133" s="40">
         <v>39.57</v>
       </c>
-      <c r="E133" s="20" t="s">
+      <c r="E133" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="F133" s="5">
+      <c r="F133" s="41">
         <v>-1</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="28"/>
+      <c r="A134" s="26"/>
       <c r="B134" s="9" t="s">
         <v>273</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D134" s="40">
         <v>44.78</v>
       </c>
-      <c r="E134" s="20" t="s">
+      <c r="E134" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="F134" s="5">
+      <c r="F134" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="28"/>
-      <c r="B135" s="13" t="s">
+      <c r="A135" s="26"/>
+      <c r="B135" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="D135" s="3">
+      <c r="D135" s="40">
         <v>43.74</v>
       </c>
-      <c r="E135" s="20" t="s">
+      <c r="E135" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="F135" s="5">
+      <c r="F135" s="41">
         <v>0</v>
       </c>
     </row>
@@ -4213,13 +4255,13 @@
       <c r="C136" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D136" s="40">
         <v>25.22</v>
       </c>
-      <c r="E136" s="20" t="s">
+      <c r="E136" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F136" s="5">
+      <c r="F136" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4233,13 +4275,13 @@
       <c r="C137" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D137" s="3">
+      <c r="D137" s="40">
         <v>52.01</v>
       </c>
-      <c r="E137" s="20" t="s">
+      <c r="E137" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="F137" s="5">
+      <c r="F137" s="41">
         <v>2</v>
       </c>
     </row>
@@ -4253,13 +4295,13 @@
       <c r="C138" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D138" s="3">
+      <c r="D138" s="40">
         <v>24.32</v>
       </c>
-      <c r="E138" s="20" t="s">
+      <c r="E138" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F138" s="5">
+      <c r="F138" s="41">
         <v>8</v>
       </c>
     </row>
@@ -4267,7 +4309,7 @@
       <c r="A139" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B139" s="27" t="s">
+      <c r="B139" s="25" t="s">
         <v>306</v>
       </c>
       <c r="C139" s="2" t="s">
@@ -4276,8 +4318,8 @@
       <c r="D139" s="5">
         <v>23.4</v>
       </c>
-      <c r="E139" s="26">
-        <v>71121040</v>
+      <c r="E139" s="24" t="s">
+        <v>369</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4287,7 +4329,7 @@
       <c r="A140" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B140" s="27" t="s">
+      <c r="B140" s="25" t="s">
         <v>307</v>
       </c>
       <c r="C140" s="2" t="s">
@@ -4296,7 +4338,7 @@
       <c r="D140" s="5">
         <v>14.37</v>
       </c>
-      <c r="E140" s="26" t="s">
+      <c r="E140" s="24" t="s">
         <v>305</v>
       </c>
       <c r="F140" s="5">
@@ -4316,7 +4358,7 @@
       <c r="D141" s="5">
         <v>17.16</v>
       </c>
-      <c r="E141" s="26" t="s">
+      <c r="E141" s="24" t="s">
         <v>349</v>
       </c>
       <c r="F141" s="5">
@@ -4327,7 +4369,7 @@
       <c r="A142" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B142" s="31" t="s">
         <v>350</v>
       </c>
       <c r="C142" s="2" t="s">
@@ -4336,7 +4378,7 @@
       <c r="D142" s="5">
         <v>29.35</v>
       </c>
-      <c r="E142" s="26" t="s">
+      <c r="E142" s="24" t="s">
         <v>351</v>
       </c>
       <c r="F142" s="5">
@@ -4356,7 +4398,7 @@
       <c r="D143" s="5">
         <v>6.01</v>
       </c>
-      <c r="E143" s="26" t="s">
+      <c r="E143" s="24" t="s">
         <v>352</v>
       </c>
       <c r="F143" s="5">
@@ -4367,1302 +4409,1302 @@
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="D144" s="5"/>
-      <c r="E144" s="15"/>
+      <c r="E144" s="13"/>
       <c r="F144" s="5"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="D145" s="5"/>
-      <c r="E145" s="15"/>
+      <c r="E145" s="13"/>
       <c r="F145" s="5"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="D146" s="5"/>
-      <c r="E146" s="15"/>
+      <c r="E146" s="13"/>
       <c r="F146" s="5"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="D147" s="5"/>
-      <c r="E147" s="15"/>
+      <c r="E147" s="13"/>
       <c r="F147" s="5"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="D148" s="5"/>
-      <c r="E148" s="15"/>
+      <c r="E148" s="13"/>
       <c r="F148" s="5"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="D149" s="5"/>
-      <c r="E149" s="15"/>
+      <c r="E149" s="13"/>
       <c r="F149" s="5"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="D150" s="5"/>
-      <c r="E150" s="15"/>
+      <c r="E150" s="13"/>
       <c r="F150" s="5"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="D151" s="5"/>
-      <c r="E151" s="15"/>
+      <c r="E151" s="13"/>
       <c r="F151" s="5"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="D152" s="5"/>
-      <c r="E152" s="15"/>
+      <c r="E152" s="13"/>
       <c r="F152" s="5"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="D153" s="5"/>
-      <c r="E153" s="15"/>
+      <c r="E153" s="13"/>
       <c r="F153" s="5"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="D154" s="5"/>
-      <c r="E154" s="15"/>
+      <c r="E154" s="13"/>
       <c r="F154" s="5"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="D155" s="5"/>
-      <c r="E155" s="15"/>
+      <c r="E155" s="13"/>
       <c r="F155" s="5"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="D156" s="5"/>
-      <c r="E156" s="15"/>
+      <c r="E156" s="13"/>
       <c r="F156" s="5"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="D157" s="5"/>
-      <c r="E157" s="15"/>
+      <c r="E157" s="13"/>
       <c r="F157" s="5"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="D158" s="5"/>
-      <c r="E158" s="15"/>
+      <c r="E158" s="13"/>
       <c r="F158" s="5"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="D159" s="5"/>
-      <c r="E159" s="15"/>
+      <c r="E159" s="13"/>
       <c r="F159" s="5"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="D160" s="5"/>
-      <c r="E160" s="15"/>
+      <c r="E160" s="13"/>
       <c r="F160" s="5"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="D161" s="5"/>
-      <c r="E161" s="15"/>
+      <c r="E161" s="13"/>
       <c r="F161" s="5"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="D162" s="5"/>
-      <c r="E162" s="15"/>
+      <c r="E162" s="13"/>
       <c r="F162" s="5"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="D163" s="5"/>
-      <c r="E163" s="15"/>
+      <c r="E163" s="13"/>
       <c r="F163" s="5"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="D164" s="5"/>
-      <c r="E164" s="15"/>
+      <c r="E164" s="13"/>
       <c r="F164" s="5"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="D165" s="5"/>
-      <c r="E165" s="15"/>
+      <c r="E165" s="13"/>
       <c r="F165" s="5"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="D166" s="5"/>
-      <c r="E166" s="15"/>
+      <c r="E166" s="13"/>
       <c r="F166" s="5"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="D167" s="5"/>
-      <c r="E167" s="15"/>
+      <c r="E167" s="13"/>
       <c r="F167" s="5"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="D168" s="5"/>
-      <c r="E168" s="15"/>
+      <c r="E168" s="13"/>
       <c r="F168" s="5"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="D169" s="5"/>
-      <c r="E169" s="15"/>
+      <c r="E169" s="13"/>
       <c r="F169" s="5"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="D170" s="5"/>
-      <c r="E170" s="15"/>
+      <c r="E170" s="13"/>
       <c r="F170" s="5"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="D171" s="5"/>
-      <c r="E171" s="15"/>
+      <c r="E171" s="13"/>
       <c r="F171" s="5"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="D172" s="5"/>
-      <c r="E172" s="15"/>
+      <c r="E172" s="13"/>
       <c r="F172" s="5"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="D173" s="5"/>
-      <c r="E173" s="15"/>
+      <c r="E173" s="13"/>
       <c r="F173" s="5"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="D174" s="5"/>
-      <c r="E174" s="15"/>
+      <c r="E174" s="13"/>
       <c r="F174" s="5"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="D175" s="5"/>
-      <c r="E175" s="15"/>
+      <c r="E175" s="13"/>
       <c r="F175" s="5"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="D176" s="5"/>
-      <c r="E176" s="15"/>
+      <c r="E176" s="13"/>
       <c r="F176" s="5"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="D177" s="5"/>
-      <c r="E177" s="15"/>
+      <c r="E177" s="13"/>
       <c r="F177" s="5"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="D178" s="5"/>
-      <c r="E178" s="15"/>
+      <c r="E178" s="13"/>
       <c r="F178" s="5"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="D179" s="5"/>
-      <c r="E179" s="15"/>
+      <c r="E179" s="13"/>
       <c r="F179" s="5"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="D180" s="5"/>
-      <c r="E180" s="15"/>
+      <c r="E180" s="13"/>
       <c r="F180" s="5"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="D181" s="5"/>
-      <c r="E181" s="15"/>
+      <c r="E181" s="13"/>
       <c r="F181" s="5"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="D182" s="5"/>
-      <c r="E182" s="15"/>
+      <c r="E182" s="13"/>
       <c r="F182" s="5"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="D183" s="5"/>
-      <c r="E183" s="15"/>
+      <c r="E183" s="13"/>
       <c r="F183" s="5"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="D184" s="5"/>
-      <c r="E184" s="15"/>
+      <c r="E184" s="13"/>
       <c r="F184" s="5"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="D185" s="5"/>
-      <c r="E185" s="15"/>
+      <c r="E185" s="13"/>
       <c r="F185" s="5"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="D186" s="5"/>
-      <c r="E186" s="15"/>
+      <c r="E186" s="13"/>
       <c r="F186" s="5"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="D187" s="5"/>
-      <c r="E187" s="15"/>
+      <c r="E187" s="13"/>
       <c r="F187" s="5"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="D188" s="5"/>
-      <c r="E188" s="15"/>
+      <c r="E188" s="13"/>
       <c r="F188" s="5"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="D189" s="5"/>
-      <c r="E189" s="15"/>
+      <c r="E189" s="13"/>
       <c r="F189" s="5"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="D190" s="5"/>
-      <c r="E190" s="15"/>
+      <c r="E190" s="13"/>
       <c r="F190" s="5"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="D191" s="5"/>
-      <c r="E191" s="15"/>
+      <c r="E191" s="13"/>
       <c r="F191" s="5"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="D192" s="5"/>
-      <c r="E192" s="15"/>
+      <c r="E192" s="13"/>
       <c r="F192" s="5"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="D193" s="5"/>
-      <c r="E193" s="15"/>
+      <c r="E193" s="13"/>
       <c r="F193" s="5"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="D194" s="5"/>
-      <c r="E194" s="15"/>
+      <c r="E194" s="13"/>
       <c r="F194" s="5"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="D195" s="5"/>
-      <c r="E195" s="15"/>
+      <c r="E195" s="13"/>
       <c r="F195" s="5"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="D196" s="5"/>
-      <c r="E196" s="15"/>
+      <c r="E196" s="13"/>
       <c r="F196" s="5"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="D197" s="5"/>
-      <c r="E197" s="15"/>
+      <c r="E197" s="13"/>
       <c r="F197" s="5"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="D198" s="5"/>
-      <c r="E198" s="15"/>
+      <c r="E198" s="13"/>
       <c r="F198" s="5"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="D199" s="5"/>
-      <c r="E199" s="15"/>
+      <c r="E199" s="13"/>
       <c r="F199" s="5"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="D200" s="5"/>
-      <c r="E200" s="15"/>
+      <c r="E200" s="13"/>
       <c r="F200" s="5"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="D201" s="5"/>
-      <c r="E201" s="15"/>
+      <c r="E201" s="13"/>
       <c r="F201" s="5"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="D202" s="5"/>
-      <c r="E202" s="15"/>
+      <c r="E202" s="13"/>
       <c r="F202" s="5"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="D203" s="5"/>
-      <c r="E203" s="15"/>
+      <c r="E203" s="13"/>
       <c r="F203" s="5"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="D204" s="5"/>
-      <c r="E204" s="15"/>
+      <c r="E204" s="13"/>
       <c r="F204" s="5"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="D205" s="5"/>
-      <c r="E205" s="15"/>
+      <c r="E205" s="13"/>
       <c r="F205" s="5"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="D206" s="5"/>
-      <c r="E206" s="15"/>
+      <c r="E206" s="13"/>
       <c r="F206" s="5"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="D207" s="5"/>
-      <c r="E207" s="15"/>
+      <c r="E207" s="13"/>
       <c r="F207" s="5"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="D208" s="5"/>
-      <c r="E208" s="15"/>
+      <c r="E208" s="13"/>
       <c r="F208" s="5"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="D209" s="5"/>
-      <c r="E209" s="15"/>
+      <c r="E209" s="13"/>
       <c r="F209" s="5"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="D210" s="5"/>
-      <c r="E210" s="15"/>
+      <c r="E210" s="13"/>
       <c r="F210" s="5"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="D211" s="5"/>
-      <c r="E211" s="15"/>
+      <c r="E211" s="13"/>
       <c r="F211" s="5"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="D212" s="5"/>
-      <c r="E212" s="15"/>
+      <c r="E212" s="13"/>
       <c r="F212" s="5"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="D213" s="5"/>
-      <c r="E213" s="15"/>
+      <c r="E213" s="13"/>
       <c r="F213" s="5"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="D214" s="5"/>
-      <c r="E214" s="15"/>
+      <c r="E214" s="13"/>
       <c r="F214" s="5"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="D215" s="5"/>
-      <c r="E215" s="15"/>
+      <c r="E215" s="13"/>
       <c r="F215" s="5"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="D216" s="5"/>
-      <c r="E216" s="15"/>
+      <c r="E216" s="13"/>
       <c r="F216" s="5"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="D217" s="5"/>
-      <c r="E217" s="15"/>
+      <c r="E217" s="13"/>
       <c r="F217" s="5"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="D218" s="5"/>
-      <c r="E218" s="15"/>
+      <c r="E218" s="13"/>
       <c r="F218" s="5"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="D219" s="5"/>
-      <c r="E219" s="15"/>
+      <c r="E219" s="13"/>
       <c r="F219" s="5"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="D220" s="5"/>
-      <c r="E220" s="15"/>
+      <c r="E220" s="13"/>
       <c r="F220" s="5"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="D221" s="5"/>
-      <c r="E221" s="15"/>
+      <c r="E221" s="13"/>
       <c r="F221" s="5"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="D222" s="5"/>
-      <c r="E222" s="15"/>
+      <c r="E222" s="13"/>
       <c r="F222" s="5"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="D223" s="5"/>
-      <c r="E223" s="15"/>
+      <c r="E223" s="13"/>
       <c r="F223" s="5"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="D224" s="5"/>
-      <c r="E224" s="15"/>
+      <c r="E224" s="13"/>
       <c r="F224" s="5"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="D225" s="5"/>
-      <c r="E225" s="15"/>
+      <c r="E225" s="13"/>
       <c r="F225" s="5"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="D226" s="5"/>
-      <c r="E226" s="15"/>
+      <c r="E226" s="13"/>
       <c r="F226" s="5"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="D227" s="5"/>
-      <c r="E227" s="15"/>
+      <c r="E227" s="13"/>
       <c r="F227" s="5"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="D228" s="5"/>
-      <c r="E228" s="15"/>
+      <c r="E228" s="13"/>
       <c r="F228" s="5"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="D229" s="5"/>
-      <c r="E229" s="15"/>
+      <c r="E229" s="13"/>
       <c r="F229" s="5"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="D230" s="5"/>
-      <c r="E230" s="15"/>
+      <c r="E230" s="13"/>
       <c r="F230" s="5"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="D231" s="5"/>
-      <c r="E231" s="15"/>
+      <c r="E231" s="13"/>
       <c r="F231" s="5"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="D232" s="5"/>
-      <c r="E232" s="15"/>
+      <c r="E232" s="13"/>
       <c r="F232" s="5"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="D233" s="5"/>
-      <c r="E233" s="15"/>
+      <c r="E233" s="13"/>
       <c r="F233" s="5"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="D234" s="5"/>
-      <c r="E234" s="15"/>
+      <c r="E234" s="13"/>
       <c r="F234" s="5"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="D235" s="5"/>
-      <c r="E235" s="15"/>
+      <c r="E235" s="13"/>
       <c r="F235" s="5"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="D236" s="5"/>
-      <c r="E236" s="15"/>
+      <c r="E236" s="13"/>
       <c r="F236" s="5"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="D237" s="5"/>
-      <c r="E237" s="15"/>
+      <c r="E237" s="13"/>
       <c r="F237" s="5"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="D238" s="5"/>
-      <c r="E238" s="15"/>
+      <c r="E238" s="13"/>
       <c r="F238" s="5"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="D239" s="5"/>
-      <c r="E239" s="15"/>
+      <c r="E239" s="13"/>
       <c r="F239" s="5"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="D240" s="5"/>
-      <c r="E240" s="15"/>
+      <c r="E240" s="13"/>
       <c r="F240" s="5"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="D241" s="5"/>
-      <c r="E241" s="15"/>
+      <c r="E241" s="13"/>
       <c r="F241" s="5"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="D242" s="5"/>
-      <c r="E242" s="15"/>
+      <c r="E242" s="13"/>
       <c r="F242" s="5"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="D243" s="5"/>
-      <c r="E243" s="15"/>
+      <c r="E243" s="13"/>
       <c r="F243" s="5"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="D244" s="5"/>
-      <c r="E244" s="15"/>
+      <c r="E244" s="13"/>
       <c r="F244" s="5"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="D245" s="5"/>
-      <c r="E245" s="15"/>
+      <c r="E245" s="13"/>
       <c r="F245" s="5"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="D246" s="5"/>
-      <c r="E246" s="15"/>
+      <c r="E246" s="13"/>
       <c r="F246" s="5"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="D247" s="5"/>
-      <c r="E247" s="15"/>
+      <c r="E247" s="13"/>
       <c r="F247" s="5"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="D248" s="5"/>
-      <c r="E248" s="15"/>
+      <c r="E248" s="13"/>
       <c r="F248" s="5"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="D249" s="5"/>
-      <c r="E249" s="15"/>
+      <c r="E249" s="13"/>
       <c r="F249" s="5"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="D250" s="5"/>
-      <c r="E250" s="15"/>
+      <c r="E250" s="13"/>
       <c r="F250" s="5"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="D251" s="5"/>
-      <c r="E251" s="15"/>
+      <c r="E251" s="13"/>
       <c r="F251" s="5"/>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="D252" s="5"/>
-      <c r="E252" s="15"/>
+      <c r="E252" s="13"/>
       <c r="F252" s="5"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="D253" s="5"/>
-      <c r="E253" s="15"/>
+      <c r="E253" s="13"/>
       <c r="F253" s="5"/>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="D254" s="5"/>
-      <c r="E254" s="15"/>
+      <c r="E254" s="13"/>
       <c r="F254" s="5"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="D255" s="5"/>
-      <c r="E255" s="15"/>
+      <c r="E255" s="13"/>
       <c r="F255" s="5"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="D256" s="5"/>
-      <c r="E256" s="15"/>
+      <c r="E256" s="13"/>
       <c r="F256" s="5"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="D257" s="5"/>
-      <c r="E257" s="15"/>
+      <c r="E257" s="13"/>
       <c r="F257" s="5"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="D258" s="5"/>
-      <c r="E258" s="15"/>
+      <c r="E258" s="13"/>
       <c r="F258" s="5"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="D259" s="5"/>
-      <c r="E259" s="15"/>
+      <c r="E259" s="13"/>
       <c r="F259" s="5"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="D260" s="5"/>
-      <c r="E260" s="15"/>
+      <c r="E260" s="13"/>
       <c r="F260" s="5"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="D261" s="5"/>
-      <c r="E261" s="15"/>
+      <c r="E261" s="13"/>
       <c r="F261" s="5"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="D262" s="5"/>
-      <c r="E262" s="15"/>
+      <c r="E262" s="13"/>
       <c r="F262" s="5"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="D263" s="5"/>
-      <c r="E263" s="15"/>
+      <c r="E263" s="13"/>
       <c r="F263" s="5"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="D264" s="5"/>
-      <c r="E264" s="15"/>
+      <c r="E264" s="13"/>
       <c r="F264" s="5"/>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="D265" s="5"/>
-      <c r="E265" s="15"/>
+      <c r="E265" s="13"/>
       <c r="F265" s="5"/>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="D266" s="5"/>
-      <c r="E266" s="15"/>
+      <c r="E266" s="13"/>
       <c r="F266" s="5"/>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="D267" s="5"/>
-      <c r="E267" s="15"/>
+      <c r="E267" s="13"/>
       <c r="F267" s="5"/>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="D268" s="5"/>
-      <c r="E268" s="15"/>
+      <c r="E268" s="13"/>
       <c r="F268" s="5"/>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="D269" s="5"/>
-      <c r="E269" s="15"/>
+      <c r="E269" s="13"/>
       <c r="F269" s="5"/>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="D270" s="5"/>
-      <c r="E270" s="15"/>
+      <c r="E270" s="13"/>
       <c r="F270" s="5"/>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="D271" s="5"/>
-      <c r="E271" s="15"/>
+      <c r="E271" s="13"/>
       <c r="F271" s="5"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="D272" s="5"/>
-      <c r="E272" s="15"/>
+      <c r="E272" s="13"/>
       <c r="F272" s="5"/>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="D273" s="5"/>
-      <c r="E273" s="15"/>
+      <c r="E273" s="13"/>
       <c r="F273" s="5"/>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="D274" s="5"/>
-      <c r="E274" s="15"/>
+      <c r="E274" s="13"/>
       <c r="F274" s="5"/>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="D275" s="5"/>
-      <c r="E275" s="15"/>
+      <c r="E275" s="13"/>
       <c r="F275" s="5"/>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="D276" s="5"/>
-      <c r="E276" s="15"/>
+      <c r="E276" s="13"/>
       <c r="F276" s="5"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="D277" s="5"/>
-      <c r="E277" s="15"/>
+      <c r="E277" s="13"/>
       <c r="F277" s="5"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="D278" s="5"/>
-      <c r="E278" s="15"/>
+      <c r="E278" s="13"/>
       <c r="F278" s="5"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="D279" s="5"/>
-      <c r="E279" s="15"/>
+      <c r="E279" s="13"/>
       <c r="F279" s="5"/>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="D280" s="5"/>
-      <c r="E280" s="15"/>
+      <c r="E280" s="13"/>
       <c r="F280" s="5"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="D281" s="5"/>
-      <c r="E281" s="15"/>
+      <c r="E281" s="13"/>
       <c r="F281" s="5"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="D282" s="5"/>
-      <c r="E282" s="15"/>
+      <c r="E282" s="13"/>
       <c r="F282" s="5"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="D283" s="5"/>
-      <c r="E283" s="15"/>
+      <c r="E283" s="13"/>
       <c r="F283" s="5"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="D284" s="5"/>
-      <c r="E284" s="15"/>
+      <c r="E284" s="13"/>
       <c r="F284" s="5"/>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="D285" s="5"/>
-      <c r="E285" s="15"/>
+      <c r="E285" s="13"/>
       <c r="F285" s="5"/>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="D286" s="5"/>
-      <c r="E286" s="15"/>
+      <c r="E286" s="13"/>
       <c r="F286" s="5"/>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="D287" s="5"/>
-      <c r="E287" s="15"/>
+      <c r="E287" s="13"/>
       <c r="F287" s="5"/>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="D288" s="5"/>
-      <c r="E288" s="15"/>
+      <c r="E288" s="13"/>
       <c r="F288" s="5"/>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="D289" s="5"/>
-      <c r="E289" s="15"/>
+      <c r="E289" s="13"/>
       <c r="F289" s="5"/>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="D290" s="5"/>
-      <c r="E290" s="15"/>
+      <c r="E290" s="13"/>
       <c r="F290" s="5"/>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="D291" s="5"/>
-      <c r="E291" s="15"/>
+      <c r="E291" s="13"/>
       <c r="F291" s="5"/>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="D292" s="5"/>
-      <c r="E292" s="15"/>
+      <c r="E292" s="13"/>
       <c r="F292" s="5"/>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="D293" s="5"/>
-      <c r="E293" s="15"/>
+      <c r="E293" s="13"/>
       <c r="F293" s="5"/>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="D294" s="5"/>
-      <c r="E294" s="15"/>
+      <c r="E294" s="13"/>
       <c r="F294" s="5"/>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="D295" s="5"/>
-      <c r="E295" s="15"/>
+      <c r="E295" s="13"/>
       <c r="F295" s="5"/>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="D296" s="5"/>
-      <c r="E296" s="15"/>
+      <c r="E296" s="13"/>
       <c r="F296" s="5"/>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="D297" s="5"/>
-      <c r="E297" s="15"/>
+      <c r="E297" s="13"/>
       <c r="F297" s="5"/>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="D298" s="5"/>
-      <c r="E298" s="15"/>
+      <c r="E298" s="13"/>
       <c r="F298" s="5"/>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="D299" s="5"/>
-      <c r="E299" s="15"/>
+      <c r="E299" s="13"/>
       <c r="F299" s="5"/>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="D300" s="5"/>
-      <c r="E300" s="15"/>
+      <c r="E300" s="13"/>
       <c r="F300" s="5"/>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="D301" s="5"/>
-      <c r="E301" s="15"/>
+      <c r="E301" s="13"/>
       <c r="F301" s="5"/>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="D302" s="5"/>
-      <c r="E302" s="15"/>
+      <c r="E302" s="13"/>
       <c r="F302" s="5"/>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="D303" s="5"/>
-      <c r="E303" s="15"/>
+      <c r="E303" s="13"/>
       <c r="F303" s="5"/>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="D304" s="5"/>
-      <c r="E304" s="15"/>
+      <c r="E304" s="13"/>
       <c r="F304" s="5"/>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="D305" s="5"/>
-      <c r="E305" s="15"/>
+      <c r="E305" s="13"/>
       <c r="F305" s="5"/>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="D306" s="5"/>
-      <c r="E306" s="15"/>
+      <c r="E306" s="13"/>
       <c r="F306" s="5"/>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="D307" s="5"/>
-      <c r="E307" s="15"/>
+      <c r="E307" s="13"/>
       <c r="F307" s="5"/>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="D308" s="5"/>
-      <c r="E308" s="15"/>
+      <c r="E308" s="13"/>
       <c r="F308" s="5"/>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="D309" s="5"/>
-      <c r="E309" s="15"/>
+      <c r="E309" s="13"/>
       <c r="F309" s="5"/>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="D310" s="5"/>
-      <c r="E310" s="15"/>
+      <c r="E310" s="13"/>
       <c r="F310" s="5"/>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="D311" s="5"/>
-      <c r="E311" s="15"/>
+      <c r="E311" s="13"/>
       <c r="F311" s="5"/>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="D312" s="5"/>
-      <c r="E312" s="15"/>
+      <c r="E312" s="13"/>
       <c r="F312" s="5"/>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="D313" s="5"/>
-      <c r="E313" s="15"/>
+      <c r="E313" s="13"/>
       <c r="F313" s="5"/>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="D314" s="5"/>
-      <c r="E314" s="15"/>
+      <c r="E314" s="13"/>
       <c r="F314" s="5"/>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="D315" s="5"/>
-      <c r="E315" s="15"/>
+      <c r="E315" s="13"/>
       <c r="F315" s="5"/>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="D316" s="5"/>
-      <c r="E316" s="15"/>
+      <c r="E316" s="13"/>
       <c r="F316" s="5"/>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="D317" s="5"/>
-      <c r="E317" s="15"/>
+      <c r="E317" s="13"/>
       <c r="F317" s="5"/>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="D318" s="5"/>
-      <c r="E318" s="15"/>
+      <c r="E318" s="13"/>
       <c r="F318" s="5"/>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="D319" s="5"/>
-      <c r="E319" s="15"/>
+      <c r="E319" s="13"/>
       <c r="F319" s="5"/>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="D320" s="5"/>
-      <c r="E320" s="15"/>
+      <c r="E320" s="13"/>
       <c r="F320" s="5"/>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="D321" s="5"/>
-      <c r="E321" s="15"/>
+      <c r="E321" s="13"/>
       <c r="F321" s="5"/>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="D322" s="5"/>
-      <c r="E322" s="15"/>
+      <c r="E322" s="13"/>
       <c r="F322" s="5"/>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="D323" s="5"/>
-      <c r="E323" s="15"/>
+      <c r="E323" s="13"/>
       <c r="F323" s="5"/>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="D324" s="5"/>
-      <c r="E324" s="15"/>
+      <c r="E324" s="13"/>
       <c r="F324" s="5"/>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="D325" s="5"/>
-      <c r="E325" s="15"/>
+      <c r="E325" s="13"/>
       <c r="F325" s="5"/>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="D326" s="5"/>
-      <c r="E326" s="15"/>
+      <c r="E326" s="13"/>
       <c r="F326" s="5"/>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="D327" s="5"/>
-      <c r="E327" s="15"/>
+      <c r="E327" s="13"/>
       <c r="F327" s="5"/>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="D328" s="5"/>
-      <c r="E328" s="15"/>
+      <c r="E328" s="13"/>
       <c r="F328" s="5"/>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="D329" s="5"/>
-      <c r="E329" s="15"/>
+      <c r="E329" s="13"/>
       <c r="F329" s="5"/>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\produits-cimentaires\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088DC4CE-7F28-461E-8A06-B9FD07402509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428094F7-A1B5-4230-A47E-26C6C772F037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23124" yWindow="12" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1832,13 +1832,13 @@
         <v>282</v>
       </c>
       <c r="D5" s="32">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="33">
-        <v>18</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1898,7 +1898,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="35">
-        <v>1053</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2023,7 +2023,7 @@
         <v>22</v>
       </c>
       <c r="F15" s="35">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2213,7 +2213,7 @@
         <v>33</v>
       </c>
       <c r="F26" s="35">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2293,7 +2293,7 @@
         <v>38</v>
       </c>
       <c r="F31" s="35">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2308,7 +2308,7 @@
         <v>39</v>
       </c>
       <c r="F32" s="35">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2328,7 +2328,7 @@
         <v>40</v>
       </c>
       <c r="F33" s="35">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2368,7 +2368,7 @@
         <v>71</v>
       </c>
       <c r="F35" s="37">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2388,7 +2388,7 @@
         <v>72</v>
       </c>
       <c r="F36" s="37">
-        <v>227</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2408,7 +2408,7 @@
         <v>73</v>
       </c>
       <c r="F37" s="37">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2428,7 +2428,7 @@
         <v>74</v>
       </c>
       <c r="F38" s="37">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2528,7 +2528,7 @@
         <v>79</v>
       </c>
       <c r="F43" s="39">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2586,7 +2586,7 @@
         <v>82</v>
       </c>
       <c r="F46" s="39">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2604,7 +2604,7 @@
         <v>83</v>
       </c>
       <c r="F47" s="39">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2710,7 +2710,7 @@
         <v>89</v>
       </c>
       <c r="F53" s="39">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2728,7 +2728,7 @@
         <v>90</v>
       </c>
       <c r="F54" s="39">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2746,7 +2746,7 @@
         <v>91</v>
       </c>
       <c r="F55" s="39">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2832,7 +2832,7 @@
         <v>96</v>
       </c>
       <c r="F60" s="39">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2852,7 +2852,7 @@
         <v>97</v>
       </c>
       <c r="F61" s="39">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2872,7 +2872,7 @@
         <v>98</v>
       </c>
       <c r="F62" s="39">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2912,7 +2912,7 @@
         <v>100</v>
       </c>
       <c r="F64" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2987,7 +2987,7 @@
         <v>104</v>
       </c>
       <c r="F68" s="41">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -3107,7 +3107,7 @@
         <v>110</v>
       </c>
       <c r="F74" s="41">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3125,7 +3125,7 @@
         <v>111</v>
       </c>
       <c r="F75" s="41">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3145,7 +3145,7 @@
         <v>112</v>
       </c>
       <c r="F76" s="41">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3205,7 +3205,7 @@
         <v>115</v>
       </c>
       <c r="F79" s="41">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -3225,7 +3225,7 @@
         <v>116</v>
       </c>
       <c r="F80" s="41">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3423,7 +3423,7 @@
         <v>126</v>
       </c>
       <c r="F90" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -3583,7 +3583,7 @@
         <v>134</v>
       </c>
       <c r="F98" s="41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -3673,7 +3673,7 @@
         <v>139</v>
       </c>
       <c r="F103" s="41">
-        <v>105</v>
+        <v>86</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -3742,7 +3742,7 @@
         <v>143</v>
       </c>
       <c r="F107" s="41">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -3757,7 +3757,7 @@
         <v>144</v>
       </c>
       <c r="F108" s="41">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -3775,7 +3775,7 @@
         <v>145</v>
       </c>
       <c r="F109" s="41">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -3793,7 +3793,7 @@
         <v>146</v>
       </c>
       <c r="F110" s="41">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -3811,7 +3811,7 @@
         <v>147</v>
       </c>
       <c r="F111" s="41">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -3829,7 +3829,7 @@
         <v>148</v>
       </c>
       <c r="F112" s="41">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -3867,7 +3867,7 @@
         <v>150</v>
       </c>
       <c r="F114" s="41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -4125,7 +4125,7 @@
         <v>164</v>
       </c>
       <c r="F128" s="41">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -4161,7 +4161,7 @@
         <v>166</v>
       </c>
       <c r="F130" s="41">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -4179,7 +4179,7 @@
         <v>167</v>
       </c>
       <c r="F131" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -4362,7 +4362,7 @@
         <v>349</v>
       </c>
       <c r="F141" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\produits-cimentaires\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428094F7-A1B5-4230-A47E-26C6C772F037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CC43F7-7213-4EED-9C56-936FF3E0D1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23124" yWindow="12" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -947,9 +947,6 @@
     <t>betons/melange-beton.png</t>
   </si>
   <si>
-    <t>betons/sakret-beton-be-25kg.png</t>
-  </si>
-  <si>
     <t>chaux/enci-mc12.5-25kg.png</t>
   </si>
   <si>
@@ -1034,9 +1031,6 @@
     <t>mortiers/knauf-mortier-refractaire.png</t>
   </si>
   <si>
-    <t>mortiers/sakret-mortier-zm-25kg.png</t>
-  </si>
-  <si>
     <t>primers/drago-paint-beton-tack.png</t>
   </si>
   <si>
@@ -1079,9 +1073,6 @@
     <t>sols/egaline-weberniv-fiber.png</t>
   </si>
   <si>
-    <t>betons/sakret-fix-beton-25kg.png</t>
-  </si>
-  <si>
     <t>mortiers/melange-mortier.png</t>
   </si>
   <si>
@@ -1146,6 +1137,15 @@
   </si>
   <si>
     <t>71121040</t>
+  </si>
+  <si>
+    <t>mortiers/knauf-mortier-25kg.png</t>
+  </si>
+  <si>
+    <t>betons/knauf-beton-25kg.png</t>
+  </si>
+  <si>
+    <t>betons/knauf-turbo-beton-25kg.png</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1363,30 +1363,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1763,7 +1739,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>9</v>
@@ -1783,7 +1759,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>10</v>
@@ -1823,7 +1799,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>41</v>
@@ -1843,7 +1819,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>42</v>
@@ -1863,7 +1839,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>43</v>
@@ -1883,7 +1859,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>44</v>
@@ -1891,13 +1867,13 @@
       <c r="C8" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="32">
         <v>7.76</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="33">
         <v>952</v>
       </c>
     </row>
@@ -1906,13 +1882,13 @@
       <c r="B9" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="32">
         <v>8.69</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="33">
         <v>0</v>
       </c>
     </row>
@@ -1921,19 +1897,19 @@
       <c r="B10" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="32">
         <v>11.370000000000001</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B11" s="20" t="s">
         <v>47</v>
@@ -1941,13 +1917,13 @@
       <c r="C11" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="32">
         <v>11.34</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="33">
         <v>30</v>
       </c>
     </row>
@@ -1956,19 +1932,19 @@
       <c r="B12" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="32">
         <v>1.8</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>49</v>
@@ -1976,19 +1952,19 @@
       <c r="C13" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="32">
         <v>7.95</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="33">
         <v>-5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B14" s="20" t="s">
         <v>50</v>
@@ -1996,19 +1972,19 @@
       <c r="C14" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="32">
         <v>15.950000000000001</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B15" s="20" t="s">
         <v>51</v>
@@ -2016,19 +1992,19 @@
       <c r="C15" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="32">
         <v>12.4</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="33">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B16" s="20" t="s">
         <v>52</v>
@@ -2036,19 +2012,19 @@
       <c r="C16" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="32">
         <v>10.620000000000001</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="33">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B17" s="20" t="s">
         <v>53</v>
@@ -2056,13 +2032,13 @@
       <c r="C17" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="32">
         <v>45.34</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2071,13 +2047,13 @@
       <c r="B18" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="32">
         <v>7.71</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2086,13 +2062,13 @@
       <c r="B19" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="32">
         <v>25.18</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2101,13 +2077,13 @@
       <c r="B20" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="32">
         <v>9.84</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2116,13 +2092,13 @@
       <c r="B21" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="32">
         <v>11.43</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2131,13 +2107,13 @@
       <c r="B22" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="32">
         <v>13.55</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2146,19 +2122,19 @@
       <c r="B23" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="32">
         <v>8.91</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B24" s="20" t="s">
         <v>60</v>
@@ -2166,19 +2142,19 @@
       <c r="C24" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="32">
         <v>12.870000000000001</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="33">
         <v>-18</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B25" s="20" t="s">
         <v>61</v>
@@ -2186,19 +2162,19 @@
       <c r="C25" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="32">
         <v>9.24</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="33">
         <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B26" s="20" t="s">
         <v>62</v>
@@ -2206,13 +2182,13 @@
       <c r="C26" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="32">
         <v>12.870000000000001</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="33">
         <v>73</v>
       </c>
     </row>
@@ -2221,13 +2197,13 @@
       <c r="B27" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="32">
         <v>10.370000000000001</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2236,13 +2212,13 @@
       <c r="B28" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="32">
         <v>10.67</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2251,13 +2227,13 @@
       <c r="B29" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="32">
         <v>8.91</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="35">
+      <c r="F29" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2266,19 +2242,19 @@
       <c r="B30" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="32">
         <v>19.52</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B31" s="20" t="s">
         <v>67</v>
@@ -2286,13 +2262,13 @@
       <c r="C31" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="32">
         <v>23.28</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="33">
         <v>102</v>
       </c>
     </row>
@@ -2301,19 +2277,19 @@
       <c r="B32" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="32">
         <v>31.470000000000002</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B33" s="20" t="s">
         <v>69</v>
@@ -2321,19 +2297,19 @@
       <c r="C33" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="32">
         <v>21.05</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="33">
         <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>175</v>
@@ -2341,19 +2317,19 @@
       <c r="C34" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="32">
         <v>5.51</v>
       </c>
       <c r="E34" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F34" s="33">
         <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="29" t="s">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>176</v>
@@ -2361,19 +2337,19 @@
       <c r="C35" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D35" s="36">
+      <c r="D35" s="32">
         <v>9</v>
       </c>
       <c r="E35" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="33">
         <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="30" t="s">
-        <v>303</v>
+        <v>368</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>177</v>
@@ -2381,19 +2357,19 @@
       <c r="C36" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D36" s="36">
+      <c r="D36" s="32">
         <v>10.74</v>
       </c>
       <c r="E36" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F36" s="33">
         <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="30" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>178</v>
@@ -2401,19 +2377,19 @@
       <c r="C37" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D37" s="36">
+      <c r="D37" s="32">
         <v>8.57</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="37">
+      <c r="F37" s="33">
         <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>179</v>
@@ -2421,19 +2397,19 @@
       <c r="C38" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D38" s="36">
+      <c r="D38" s="32">
         <v>7.5</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="37">
+      <c r="F38" s="33">
         <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>180</v>
@@ -2441,19 +2417,19 @@
       <c r="C39" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D39" s="36">
+      <c r="D39" s="32">
         <v>6.98</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="37">
+      <c r="F39" s="33">
         <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>181</v>
@@ -2473,7 +2449,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>182</v>
@@ -2481,13 +2457,13 @@
       <c r="C41" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D41" s="38">
+      <c r="D41" s="32">
         <v>10.35</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F41" s="39">
+      <c r="F41" s="33">
         <v>-4</v>
       </c>
     </row>
@@ -2501,19 +2477,19 @@
       <c r="C42" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D42" s="38">
+      <c r="D42" s="32">
         <v>46.52</v>
       </c>
       <c r="E42" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F42" s="39">
+      <c r="F42" s="33">
         <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>184</v>
@@ -2521,19 +2497,19 @@
       <c r="C43" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D43" s="38">
+      <c r="D43" s="32">
         <v>11</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="F43" s="39">
+      <c r="F43" s="33">
         <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>185</v>
@@ -2541,19 +2517,19 @@
       <c r="C44" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="32">
         <v>52.19</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="39">
+      <c r="F44" s="33">
         <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>186</v>
@@ -2561,13 +2537,13 @@
       <c r="C45" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D45" s="38">
+      <c r="D45" s="32">
         <v>87.74</v>
       </c>
       <c r="E45" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F45" s="39">
+      <c r="F45" s="33">
         <v>5</v>
       </c>
     </row>
@@ -2579,13 +2555,13 @@
       <c r="C46" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D46" s="38">
+      <c r="D46" s="32">
         <v>15.13</v>
       </c>
       <c r="E46" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F46" s="39">
+      <c r="F46" s="33">
         <v>7</v>
       </c>
     </row>
@@ -2597,19 +2573,19 @@
       <c r="C47" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D47" s="38">
+      <c r="D47" s="32">
         <v>43.63</v>
       </c>
       <c r="E47" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="F47" s="39">
+      <c r="F47" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>189</v>
@@ -2617,19 +2593,19 @@
       <c r="C48" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D48" s="38">
+      <c r="D48" s="32">
         <v>14.59</v>
       </c>
       <c r="E48" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F48" s="39">
+      <c r="F48" s="33">
         <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>190</v>
@@ -2637,13 +2613,13 @@
       <c r="C49" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D49" s="38">
+      <c r="D49" s="32">
         <v>36.869999999999997</v>
       </c>
       <c r="E49" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F49" s="39">
+      <c r="F49" s="33">
         <v>4</v>
       </c>
     </row>
@@ -2653,13 +2629,13 @@
         <v>191</v>
       </c>
       <c r="C50" s="28"/>
-      <c r="D50" s="38">
+      <c r="D50" s="32">
         <v>24.14</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="F50" s="39">
+      <c r="F50" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2669,13 +2645,13 @@
         <v>192</v>
       </c>
       <c r="C51" s="28"/>
-      <c r="D51" s="38">
+      <c r="D51" s="32">
         <v>12.46</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="F51" s="39">
+      <c r="F51" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2685,13 +2661,13 @@
         <v>193</v>
       </c>
       <c r="C52" s="28"/>
-      <c r="D52" s="38">
+      <c r="D52" s="32">
         <v>60.84</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F52" s="39">
+      <c r="F52" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2703,13 +2679,13 @@
       <c r="C53" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D53" s="38">
+      <c r="D53" s="32">
         <v>28.75</v>
       </c>
       <c r="E53" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F53" s="39">
+      <c r="F53" s="33">
         <v>15</v>
       </c>
     </row>
@@ -2721,13 +2697,13 @@
       <c r="C54" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D54" s="38">
+      <c r="D54" s="32">
         <v>58.82</v>
       </c>
       <c r="E54" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="F54" s="39">
+      <c r="F54" s="33">
         <v>11</v>
       </c>
     </row>
@@ -2739,13 +2715,13 @@
       <c r="C55" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D55" s="38">
+      <c r="D55" s="32">
         <v>23.490000000000002</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F55" s="39">
+      <c r="F55" s="33">
         <v>7</v>
       </c>
     </row>
@@ -2757,13 +2733,13 @@
       <c r="C56" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D56" s="38">
+      <c r="D56" s="32">
         <v>59.9</v>
       </c>
       <c r="E56" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F56" s="39">
+      <c r="F56" s="33">
         <v>8</v>
       </c>
     </row>
@@ -2773,13 +2749,13 @@
         <v>198</v>
       </c>
       <c r="C57" s="28"/>
-      <c r="D57" s="38">
+      <c r="D57" s="32">
         <v>8.36</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F57" s="39">
+      <c r="F57" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2789,13 +2765,13 @@
         <v>199</v>
       </c>
       <c r="C58" s="28"/>
-      <c r="D58" s="38">
+      <c r="D58" s="32">
         <v>33.200000000000003</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="F58" s="39">
+      <c r="F58" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2805,19 +2781,19 @@
         <v>200</v>
       </c>
       <c r="C59" s="28"/>
-      <c r="D59" s="38">
+      <c r="D59" s="32">
         <v>39.57</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="F59" s="39">
+      <c r="F59" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>201</v>
@@ -2825,19 +2801,19 @@
       <c r="C60" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D60" s="38">
+      <c r="D60" s="32">
         <v>18.5</v>
       </c>
       <c r="E60" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F60" s="39">
+      <c r="F60" s="33">
         <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>202</v>
@@ -2845,19 +2821,19 @@
       <c r="C61" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D61" s="38">
+      <c r="D61" s="32">
         <v>20.990000000000002</v>
       </c>
       <c r="E61" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F61" s="39">
+      <c r="F61" s="33">
         <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>203</v>
@@ -2865,19 +2841,19 @@
       <c r="C62" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D62" s="38">
+      <c r="D62" s="32">
         <v>48.1</v>
       </c>
       <c r="E62" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F62" s="39">
+      <c r="F62" s="33">
         <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>204</v>
@@ -2885,19 +2861,19 @@
       <c r="C63" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D63" s="38">
+      <c r="D63" s="32">
         <v>51.81</v>
       </c>
       <c r="E63" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="F63" s="39">
+      <c r="F63" s="33">
         <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>205</v>
@@ -2905,19 +2881,19 @@
       <c r="C64" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D64" s="40">
+      <c r="D64" s="32">
         <v>65.8</v>
       </c>
       <c r="E64" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F64" s="41">
+      <c r="F64" s="33">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>206</v>
@@ -2925,13 +2901,13 @@
       <c r="C65" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D65" s="40">
+      <c r="D65" s="32">
         <v>129.94999999999999</v>
       </c>
       <c r="E65" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="F65" s="41">
+      <c r="F65" s="33">
         <v>2</v>
       </c>
     </row>
@@ -2940,19 +2916,19 @@
       <c r="B66" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="D66" s="40">
+      <c r="D66" s="32">
         <v>255.92000000000002</v>
       </c>
       <c r="E66" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F66" s="41">
+      <c r="F66" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>207</v>
@@ -2960,153 +2936,153 @@
       <c r="C67" s="2">
         <v>100</v>
       </c>
-      <c r="D67" s="40">
+      <c r="D67" s="32">
         <v>11.8</v>
       </c>
       <c r="E67" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F67" s="41">
+      <c r="F67" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>208</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D68" s="40">
+        <v>356</v>
+      </c>
+      <c r="D68" s="32">
         <v>13.16</v>
       </c>
       <c r="E68" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="F68" s="41">
+      <c r="F68" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>209</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D69" s="40">
+        <v>357</v>
+      </c>
+      <c r="D69" s="32">
         <v>13.36</v>
       </c>
       <c r="E69" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F69" s="41">
+      <c r="F69" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>210</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D70" s="40">
+        <v>358</v>
+      </c>
+      <c r="D70" s="32">
         <v>13.36</v>
       </c>
       <c r="E70" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F70" s="41">
+      <c r="F70" s="33">
         <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>211</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D71" s="40">
+        <v>359</v>
+      </c>
+      <c r="D71" s="32">
         <v>14.14</v>
       </c>
       <c r="E71" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F71" s="41">
+      <c r="F71" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>212</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D72" s="40">
+        <v>360</v>
+      </c>
+      <c r="D72" s="32">
         <v>12.780000000000001</v>
       </c>
       <c r="E72" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F72" s="41">
+      <c r="F72" s="33">
         <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>213</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D73" s="40">
+        <v>361</v>
+      </c>
+      <c r="D73" s="32">
         <v>13.200000000000001</v>
       </c>
       <c r="E73" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F73" s="41">
+      <c r="F73" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>214</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D74" s="40">
+        <v>362</v>
+      </c>
+      <c r="D74" s="32">
         <v>14.35</v>
       </c>
       <c r="E74" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="F74" s="41">
+      <c r="F74" s="33">
         <v>6</v>
       </c>
     </row>
@@ -3118,277 +3094,277 @@
       <c r="C75" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="D75" s="40">
+      <c r="D75" s="32">
         <v>31.02</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="F75" s="41">
+      <c r="F75" s="33">
         <v>-3</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>216</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="D76" s="40">
+        <v>363</v>
+      </c>
+      <c r="D76" s="32">
         <v>24.88</v>
       </c>
       <c r="E76" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F76" s="41">
+      <c r="F76" s="33">
         <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>217</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D77" s="40">
+        <v>364</v>
+      </c>
+      <c r="D77" s="32">
         <v>28.64</v>
       </c>
       <c r="E77" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F77" s="41">
+      <c r="F77" s="33">
         <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>218</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D78" s="40">
+        <v>362</v>
+      </c>
+      <c r="D78" s="32">
         <v>28.22</v>
       </c>
       <c r="E78" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="F78" s="41">
+      <c r="F78" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>219</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D79" s="40">
+        <v>358</v>
+      </c>
+      <c r="D79" s="32">
         <v>28.650000000000002</v>
       </c>
       <c r="E79" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F79" s="41">
+      <c r="F79" s="33">
         <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>220</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D80" s="40">
+        <v>356</v>
+      </c>
+      <c r="D80" s="32">
         <v>20.61</v>
       </c>
       <c r="E80" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="F80" s="41">
+      <c r="F80" s="33">
         <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>221</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D81" s="40">
+        <v>359</v>
+      </c>
+      <c r="D81" s="32">
         <v>28.25</v>
       </c>
       <c r="E81" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="F81" s="41">
+      <c r="F81" s="33">
         <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>222</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D82" s="40">
+        <v>360</v>
+      </c>
+      <c r="D82" s="32">
         <v>25.92</v>
       </c>
       <c r="E82" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="F82" s="41">
+      <c r="F82" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>223</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D83" s="40">
+        <v>361</v>
+      </c>
+      <c r="D83" s="32">
         <v>27.87</v>
       </c>
       <c r="E83" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="F83" s="41">
+      <c r="F83" s="33">
         <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>224</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D84" s="40">
+        <v>357</v>
+      </c>
+      <c r="D84" s="32">
         <v>28.64</v>
       </c>
       <c r="E84" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="F84" s="41">
+      <c r="F84" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B85" s="9" t="s">
         <v>225</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D85" s="40">
+        <v>365</v>
+      </c>
+      <c r="D85" s="32">
         <v>19.7</v>
       </c>
       <c r="E85" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="F85" s="41">
+      <c r="F85" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>226</v>
       </c>
       <c r="C86" s="28"/>
-      <c r="D86" s="40">
+      <c r="D86" s="32">
         <v>79.86</v>
       </c>
       <c r="E86" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F86" s="41">
+      <c r="F86" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>227</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D87" s="40">
+        <v>362</v>
+      </c>
+      <c r="D87" s="32">
         <v>111.09</v>
       </c>
       <c r="E87" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="F87" s="41">
+      <c r="F87" s="33">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B88" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="B88" s="9" t="s">
-        <v>317</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D88" s="40">
+        <v>356</v>
+      </c>
+      <c r="D88" s="32">
         <v>79.92</v>
       </c>
       <c r="E88" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F88" s="41">
+      <c r="F88" s="33">
         <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>228</v>
@@ -3396,19 +3372,19 @@
       <c r="C89" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D89" s="40">
+      <c r="D89" s="32">
         <v>20.7</v>
       </c>
       <c r="E89" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="F89" s="41">
+      <c r="F89" s="33">
         <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>229</v>
@@ -3416,19 +3392,19 @@
       <c r="C90" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D90" s="40">
+      <c r="D90" s="32">
         <v>56</v>
       </c>
       <c r="E90" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F90" s="41">
+      <c r="F90" s="33">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>230</v>
@@ -3436,19 +3412,19 @@
       <c r="C91" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D91" s="40">
+      <c r="D91" s="32">
         <v>112</v>
       </c>
       <c r="E91" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="F91" s="41">
+      <c r="F91" s="33">
         <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B92" s="9" t="s">
         <v>231</v>
@@ -3456,19 +3432,19 @@
       <c r="C92" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D92" s="40">
+      <c r="D92" s="32">
         <v>64.17</v>
       </c>
       <c r="E92" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F92" s="41">
+      <c r="F92" s="33">
         <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B93" s="9" t="s">
         <v>232</v>
@@ -3476,19 +3452,19 @@
       <c r="C93" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D93" s="40">
+      <c r="D93" s="32">
         <v>12.68</v>
       </c>
       <c r="E93" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F93" s="41">
+      <c r="F93" s="33">
         <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B94" s="9" t="s">
         <v>233</v>
@@ -3496,19 +3472,19 @@
       <c r="C94" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D94" s="40">
+      <c r="D94" s="32">
         <v>12.91</v>
       </c>
       <c r="E94" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="F94" s="41">
+      <c r="F94" s="33">
         <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B95" s="9" t="s">
         <v>234</v>
@@ -3516,19 +3492,19 @@
       <c r="C95" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D95" s="40">
+      <c r="D95" s="32">
         <v>27.330000000000002</v>
       </c>
       <c r="E95" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F95" s="41">
+      <c r="F95" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>235</v>
@@ -3536,19 +3512,19 @@
       <c r="C96" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D96" s="40">
+      <c r="D96" s="32">
         <v>33.5</v>
       </c>
       <c r="E96" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F96" s="41">
+      <c r="F96" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B97" s="9" t="s">
         <v>236</v>
@@ -3556,19 +3532,19 @@
       <c r="C97" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D97" s="40">
+      <c r="D97" s="32">
         <v>38.880000000000003</v>
       </c>
       <c r="E97" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="F97" s="41">
+      <c r="F97" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>237</v>
@@ -3576,19 +3552,19 @@
       <c r="C98" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D98" s="40">
+      <c r="D98" s="32">
         <v>8.66</v>
       </c>
       <c r="E98" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F98" s="41">
+      <c r="F98" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>238</v>
@@ -3596,13 +3572,13 @@
       <c r="C99" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D99" s="40">
+      <c r="D99" s="32">
         <v>69.650000000000006</v>
       </c>
       <c r="E99" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="F99" s="41">
+      <c r="F99" s="33">
         <v>2</v>
       </c>
     </row>
@@ -3611,19 +3587,19 @@
       <c r="B100" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="D100" s="40">
+      <c r="D100" s="32">
         <v>24.650000000000002</v>
       </c>
       <c r="E100" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="F100" s="41">
+      <c r="F100" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>240</v>
@@ -3631,13 +3607,13 @@
       <c r="C101" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D101" s="40">
+      <c r="D101" s="32">
         <v>47.19</v>
       </c>
       <c r="E101" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="F101" s="41">
+      <c r="F101" s="33">
         <v>3</v>
       </c>
     </row>
@@ -3646,19 +3622,19 @@
       <c r="B102" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="D102" s="40">
+      <c r="D102" s="32">
         <v>29.080000000000002</v>
       </c>
       <c r="E102" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="F102" s="41">
+      <c r="F102" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>242</v>
@@ -3666,13 +3642,13 @@
       <c r="C103" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D103" s="40">
+      <c r="D103" s="32">
         <v>32.69</v>
       </c>
       <c r="E103" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="F103" s="41">
+      <c r="F103" s="33">
         <v>86</v>
       </c>
     </row>
@@ -3684,13 +3660,13 @@
       <c r="C104" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D104" s="40">
+      <c r="D104" s="32">
         <v>24.26</v>
       </c>
       <c r="E104" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="F104" s="41">
+      <c r="F104" s="33">
         <v>6</v>
       </c>
     </row>
@@ -3702,13 +3678,13 @@
       <c r="C105" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D105" s="40">
+      <c r="D105" s="32">
         <v>23.1</v>
       </c>
       <c r="E105" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="F105" s="41">
+      <c r="F105" s="33">
         <v>5</v>
       </c>
     </row>
@@ -3720,13 +3696,13 @@
       <c r="C106" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D106" s="40">
+      <c r="D106" s="32">
         <v>7.8</v>
       </c>
       <c r="E106" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F106" s="41">
+      <c r="F106" s="33">
         <v>4</v>
       </c>
     </row>
@@ -3735,13 +3711,13 @@
       <c r="B107" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="D107" s="40">
+      <c r="D107" s="32">
         <v>7.51</v>
       </c>
       <c r="E107" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="F107" s="41">
+      <c r="F107" s="33">
         <v>16</v>
       </c>
     </row>
@@ -3750,13 +3726,13 @@
       <c r="B108" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="D108" s="40">
+      <c r="D108" s="32">
         <v>17.16</v>
       </c>
       <c r="E108" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="F108" s="41">
+      <c r="F108" s="33">
         <v>4</v>
       </c>
     </row>
@@ -3768,13 +3744,13 @@
       <c r="C109" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D109" s="40">
+      <c r="D109" s="32">
         <v>16.5</v>
       </c>
       <c r="E109" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="F109" s="41">
+      <c r="F109" s="33">
         <v>1</v>
       </c>
     </row>
@@ -3786,13 +3762,13 @@
       <c r="C110" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D110" s="40">
+      <c r="D110" s="32">
         <v>8.4499999999999993</v>
       </c>
       <c r="E110" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F110" s="41">
+      <c r="F110" s="33">
         <v>28</v>
       </c>
     </row>
@@ -3804,13 +3780,13 @@
       <c r="C111" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D111" s="40">
+      <c r="D111" s="32">
         <v>30.66</v>
       </c>
       <c r="E111" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="F111" s="41">
+      <c r="F111" s="33">
         <v>17</v>
       </c>
     </row>
@@ -3822,13 +3798,13 @@
       <c r="C112" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D112" s="40">
+      <c r="D112" s="32">
         <v>32.44</v>
       </c>
       <c r="E112" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F112" s="41">
+      <c r="F112" s="33">
         <v>13</v>
       </c>
     </row>
@@ -3840,19 +3816,19 @@
       <c r="C113" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D113" s="40">
+      <c r="D113" s="32">
         <v>8.86</v>
       </c>
       <c r="E113" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="F113" s="41">
+      <c r="F113" s="33">
         <v>-1</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>253</v>
@@ -3860,19 +3836,19 @@
       <c r="C114" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D114" s="40">
+      <c r="D114" s="32">
         <v>19.02</v>
       </c>
       <c r="E114" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F114" s="41">
+      <c r="F114" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>254</v>
@@ -3880,13 +3856,13 @@
       <c r="C115" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D115" s="40">
+      <c r="D115" s="32">
         <v>51.44</v>
       </c>
       <c r="E115" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="F115" s="41">
+      <c r="F115" s="33">
         <v>1</v>
       </c>
     </row>
@@ -3898,19 +3874,19 @@
       <c r="C116" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D116" s="40">
+      <c r="D116" s="32">
         <v>11.58</v>
       </c>
       <c r="E116" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="F116" s="41">
+      <c r="F116" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B117" s="9" t="s">
         <v>256</v>
@@ -3918,19 +3894,19 @@
       <c r="C117" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D117" s="40">
+      <c r="D117" s="32">
         <v>35.56</v>
       </c>
       <c r="E117" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="F117" s="41">
+      <c r="F117" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B118" s="9" t="s">
         <v>257</v>
@@ -3938,13 +3914,13 @@
       <c r="C118" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D118" s="40">
+      <c r="D118" s="32">
         <v>89.14</v>
       </c>
       <c r="E118" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="F118" s="41">
+      <c r="F118" s="33">
         <v>4</v>
       </c>
     </row>
@@ -3956,13 +3932,13 @@
       <c r="C119" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D119" s="40">
+      <c r="D119" s="32">
         <v>24.32</v>
       </c>
       <c r="E119" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="F119" s="41">
+      <c r="F119" s="33">
         <v>5</v>
       </c>
     </row>
@@ -3974,13 +3950,13 @@
       <c r="C120" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D120" s="40">
+      <c r="D120" s="32">
         <v>31.240000000000002</v>
       </c>
       <c r="E120" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="F120" s="41">
+      <c r="F120" s="33">
         <v>4</v>
       </c>
     </row>
@@ -3992,13 +3968,13 @@
       <c r="C121" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D121" s="40">
+      <c r="D121" s="32">
         <v>28.82</v>
       </c>
       <c r="E121" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="F121" s="41">
+      <c r="F121" s="33">
         <v>4</v>
       </c>
     </row>
@@ -4010,13 +3986,13 @@
       <c r="C122" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D122" s="40">
+      <c r="D122" s="32">
         <v>72.710000000000008</v>
       </c>
       <c r="E122" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="F122" s="41">
+      <c r="F122" s="33">
         <v>3</v>
       </c>
     </row>
@@ -4028,13 +4004,13 @@
       <c r="C123" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D123" s="40">
+      <c r="D123" s="32">
         <v>9.64</v>
       </c>
       <c r="E123" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="F123" s="41">
+      <c r="F123" s="33">
         <v>0</v>
       </c>
     </row>
@@ -4046,13 +4022,13 @@
       <c r="C124" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D124" s="40">
+      <c r="D124" s="32">
         <v>23.8</v>
       </c>
       <c r="E124" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="F124" s="41">
+      <c r="F124" s="33">
         <v>3</v>
       </c>
     </row>
@@ -4064,13 +4040,13 @@
       <c r="C125" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D125" s="40">
+      <c r="D125" s="32">
         <v>35.68</v>
       </c>
       <c r="E125" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="F125" s="41">
+      <c r="F125" s="33">
         <v>0</v>
       </c>
     </row>
@@ -4082,13 +4058,13 @@
       <c r="C126" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D126" s="40">
+      <c r="D126" s="32">
         <v>18.22</v>
       </c>
       <c r="E126" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="F126" s="41">
+      <c r="F126" s="33">
         <v>12</v>
       </c>
     </row>
@@ -4100,13 +4076,13 @@
       <c r="C127" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D127" s="40">
+      <c r="D127" s="32">
         <v>18.150000000000002</v>
       </c>
       <c r="E127" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F127" s="41">
+      <c r="F127" s="33">
         <v>3</v>
       </c>
     </row>
@@ -4118,13 +4094,13 @@
       <c r="C128" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D128" s="40">
+      <c r="D128" s="32">
         <v>15.32</v>
       </c>
       <c r="E128" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F128" s="41">
+      <c r="F128" s="33">
         <v>19</v>
       </c>
     </row>
@@ -4136,13 +4112,13 @@
       <c r="C129" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D129" s="40">
+      <c r="D129" s="32">
         <v>29.5</v>
       </c>
       <c r="E129" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="F129" s="41">
+      <c r="F129" s="33">
         <v>3</v>
       </c>
     </row>
@@ -4154,13 +4130,13 @@
       <c r="C130" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D130" s="40">
+      <c r="D130" s="32">
         <v>44</v>
       </c>
       <c r="E130" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="F130" s="41">
+      <c r="F130" s="33">
         <v>22</v>
       </c>
     </row>
@@ -4172,13 +4148,13 @@
       <c r="C131" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D131" s="40">
+      <c r="D131" s="32">
         <v>64</v>
       </c>
       <c r="E131" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F131" s="41">
+      <c r="F131" s="33">
         <v>1</v>
       </c>
     </row>
@@ -4187,13 +4163,13 @@
       <c r="B132" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="D132" s="40">
+      <c r="D132" s="32">
         <v>18.37</v>
       </c>
       <c r="E132" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="F132" s="41">
+      <c r="F132" s="33">
         <v>0</v>
       </c>
     </row>
@@ -4202,13 +4178,13 @@
       <c r="B133" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D133" s="40">
+      <c r="D133" s="32">
         <v>39.57</v>
       </c>
       <c r="E133" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="F133" s="41">
+      <c r="F133" s="33">
         <v>-1</v>
       </c>
     </row>
@@ -4220,13 +4196,13 @@
       <c r="C134" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D134" s="40">
+      <c r="D134" s="32">
         <v>44.78</v>
       </c>
       <c r="E134" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="F134" s="41">
+      <c r="F134" s="33">
         <v>1</v>
       </c>
     </row>
@@ -4235,19 +4211,19 @@
       <c r="B135" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="D135" s="40">
+      <c r="D135" s="32">
         <v>43.74</v>
       </c>
       <c r="E135" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="F135" s="41">
+      <c r="F135" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B136" s="9" t="s">
         <v>275</v>
@@ -4255,19 +4231,19 @@
       <c r="C136" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D136" s="40">
+      <c r="D136" s="32">
         <v>25.22</v>
       </c>
       <c r="E136" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F136" s="41">
+      <c r="F136" s="33">
         <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B137" s="9" t="s">
         <v>276</v>
@@ -4275,19 +4251,19 @@
       <c r="C137" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D137" s="40">
+      <c r="D137" s="32">
         <v>52.01</v>
       </c>
       <c r="E137" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="F137" s="41">
+      <c r="F137" s="33">
         <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B138" s="9" t="s">
         <v>277</v>
@@ -4295,22 +4271,22 @@
       <c r="C138" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D138" s="40">
+      <c r="D138" s="32">
         <v>24.32</v>
       </c>
       <c r="E138" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F138" s="41">
+      <c r="F138" s="33">
         <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B139" s="25" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>279</v>
@@ -4319,7 +4295,7 @@
         <v>23.4</v>
       </c>
       <c r="E139" s="24" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4327,10 +4303,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B140" s="25" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>279</v>
@@ -4339,7 +4315,7 @@
         <v>14.37</v>
       </c>
       <c r="E140" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F140" s="5">
         <v>5</v>
@@ -4347,10 +4323,10 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>287</v>
@@ -4359,7 +4335,7 @@
         <v>17.16</v>
       </c>
       <c r="E141" s="24" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F141" s="5">
         <v>3</v>
@@ -4367,10 +4343,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B142" s="31" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>287</v>
@@ -4379,7 +4355,7 @@
         <v>29.35</v>
       </c>
       <c r="E142" s="24" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F142" s="5">
         <v>6</v>
@@ -4387,10 +4363,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>286</v>
@@ -4399,7 +4375,7 @@
         <v>6.01</v>
       </c>
       <c r="E143" s="24" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F143" s="5">
         <v>20</v>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\produits-cimentaires\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CC43F7-7213-4EED-9C56-936FF3E0D1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA6140C-90AC-4181-84BE-CDF127532B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="372">
   <si>
     <t>path</t>
   </si>
@@ -257,9 +257,6 @@
     <t>71140904</t>
   </si>
   <si>
-    <t>71140907</t>
-  </si>
-  <si>
     <t>71140912</t>
   </si>
   <si>
@@ -569,12 +566,6 @@
     <t>Mortier sec  25 kg (ZM)</t>
   </si>
   <si>
-    <t>Beton préparé BE 25 kg</t>
-  </si>
-  <si>
-    <t>Fix Beton Sakret 25kg SF</t>
-  </si>
-  <si>
     <t>chape 25kg</t>
   </si>
   <si>
@@ -1146,6 +1137,21 @@
   </si>
   <si>
     <t>betons/knauf-turbo-beton-25kg.png</t>
+  </si>
+  <si>
+    <t>711409021</t>
+  </si>
+  <si>
+    <t>71140905</t>
+  </si>
+  <si>
+    <t>Mortier préparé KNAUF 25 kg</t>
+  </si>
+  <si>
+    <t>Beton préparé 25 kg</t>
+  </si>
+  <si>
+    <t>Beton turbo 25kg</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1191,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1200,43 +1206,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1258,6 +1228,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1271,7 +1265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1298,55 +1292,19 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1361,7 +1319,62 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1704,14 +1717,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065E4AF0-A4F8-4CE3-9E23-EDCEACB756BD}">
-  <dimension ref="A1:G332"/>
+  <dimension ref="A1:G333"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.77734375" style="5" customWidth="1"/>
   </cols>
@@ -1723,13 +1736,13 @@
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
@@ -1739,38 +1752,38 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="B2" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D2" s="3">
         <v>28.48</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="5">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="B3" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D3" s="3">
         <v>52.83</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="36" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="5">
@@ -1779,2583 +1792,2589 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B4" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D4" s="3">
         <v>74.100000000000009</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5">
-        <v>1</v>
+        <v>16.151</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="B5" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D5" s="32">
+        <v>279</v>
+      </c>
+      <c r="D5" s="19">
         <v>31</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="33">
-        <v>45</v>
+      <c r="F5" s="20">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="B6" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D6" s="32">
+        <v>277</v>
+      </c>
+      <c r="D6" s="19">
         <v>41.71</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="20">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="B7" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D7" s="32">
+        <v>280</v>
+      </c>
+      <c r="D7" s="19">
         <v>74.62</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="20">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B8" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D8" s="32">
+        <v>276</v>
+      </c>
+      <c r="D8" s="21">
         <v>7.76</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="33">
-        <v>952</v>
+      <c r="F8" s="22">
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="21">
         <v>8.69</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="21">
         <v>11.370000000000001</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B11" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D11" s="32">
+        <v>276</v>
+      </c>
+      <c r="D11" s="21">
         <v>11.34</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="33">
-        <v>30</v>
+      <c r="F11" s="22">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="21">
         <v>1.8</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B13" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D13" s="32">
+        <v>277</v>
+      </c>
+      <c r="D13" s="21">
         <v>7.95</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="22">
         <v>-5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B14" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>50</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D14" s="32">
+        <v>276</v>
+      </c>
+      <c r="D14" s="21">
         <v>15.950000000000001</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="22">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="B15" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D15" s="32">
+        <v>277</v>
+      </c>
+      <c r="D15" s="21">
         <v>12.4</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="33">
-        <v>8</v>
+      <c r="F15" s="22">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D16" s="32">
+        <v>277</v>
+      </c>
+      <c r="D16" s="21">
         <v>10.620000000000001</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="33">
-        <v>1</v>
+      <c r="F16" s="22">
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B17" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>53</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D17" s="32">
+        <v>276</v>
+      </c>
+      <c r="D17" s="21">
         <v>45.34</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="21" t="s">
+      <c r="A18" s="14"/>
+      <c r="B18" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="21">
         <v>7.71</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="21" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="21">
         <v>25.18</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="21" t="s">
+      <c r="A20" s="14"/>
+      <c r="B20" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="21">
         <v>9.84</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="21" t="s">
+      <c r="A21" s="14"/>
+      <c r="B21" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="21">
         <v>11.43</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="26"/>
-      <c r="B22" s="21" t="s">
+      <c r="A22" s="14"/>
+      <c r="B22" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="21">
         <v>13.55</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="20" t="s">
+      <c r="A23" s="14"/>
+      <c r="B23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="21">
         <v>8.91</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="B24" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D24" s="32">
+        <v>281</v>
+      </c>
+      <c r="D24" s="21">
         <v>12.870000000000001</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="33">
-        <v>-18</v>
+      <c r="F24" s="22">
+        <v>-89</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="B25" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D25" s="32">
+        <v>281</v>
+      </c>
+      <c r="D25" s="21">
         <v>9.24</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="22">
         <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="B26" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D26" s="32">
+        <v>281</v>
+      </c>
+      <c r="D26" s="21">
         <v>12.870000000000001</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="33">
-        <v>73</v>
+      <c r="F26" s="22">
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="21" t="s">
+      <c r="A27" s="14"/>
+      <c r="B27" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="21">
         <v>10.370000000000001</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
-      <c r="B28" s="21" t="s">
+      <c r="A28" s="14"/>
+      <c r="B28" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="21">
         <v>10.67</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="20" t="s">
+      <c r="A29" s="14"/>
+      <c r="B29" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="21">
         <v>8.91</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="21" t="s">
+      <c r="A30" s="14"/>
+      <c r="B30" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="21">
         <v>19.52</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="B31" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D31" s="21">
+        <v>23.28</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="22">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="14"/>
+      <c r="B32" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="21">
+        <v>31.470000000000002</v>
+      </c>
+      <c r="E32" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D33" s="21">
+        <v>21.05</v>
+      </c>
+      <c r="E33" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="22">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D34" s="26">
+        <v>5.51</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="27">
+        <v>13</v>
+      </c>
+      <c r="G34" s="24"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D35" s="26">
+        <v>9</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="27">
+        <v>0</v>
+      </c>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="36" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="17"/>
+      <c r="B36" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D36" s="26">
+        <v>5.18</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="F36" s="27">
+        <v>293</v>
+      </c>
+      <c r="G36" s="24"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D37" s="26">
+        <v>6.95</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="27">
+        <v>161</v>
+      </c>
+      <c r="G37" s="24"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D38" s="26">
+        <v>8.57</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="F38" s="27">
+        <v>137</v>
+      </c>
+      <c r="G38" s="24"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D39" s="26">
+        <v>7.5</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="27">
+        <v>102</v>
+      </c>
+      <c r="G39" s="24"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" s="26">
+        <v>6.98</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F40" s="27">
+        <v>52</v>
+      </c>
+      <c r="G40" s="24"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D41" s="3">
+        <v>6.6400000000000006</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="5">
+        <v>10</v>
+      </c>
+      <c r="G41" s="24"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D42" s="28">
+        <v>10.35</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="29">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D43" s="28">
+        <v>46.52</v>
+      </c>
+      <c r="E43" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D44" s="28">
+        <v>11</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="F44" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D45" s="28">
+        <v>52.19</v>
+      </c>
+      <c r="E45" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F45" s="29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D31" s="32">
-        <v>23.28</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="33">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="32">
-        <v>31.470000000000002</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D33" s="32">
-        <v>21.05</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="33">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D34" s="32">
-        <v>5.51</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="F34" s="33">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D35" s="32">
-        <v>9</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="33">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="30" t="s">
-        <v>368</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D36" s="32">
-        <v>10.74</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F36" s="33">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D37" s="32">
-        <v>8.57</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F37" s="33">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D38" s="32">
-        <v>7.5</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F38" s="33">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D39" s="32">
-        <v>6.98</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" s="33">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D40" s="3">
-        <v>6.6400000000000006</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D41" s="32">
-        <v>10.35</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F41" s="33">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D42" s="32">
-        <v>46.52</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F42" s="33">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="B43" s="10" t="s">
+      <c r="D46" s="28">
+        <v>87.74</v>
+      </c>
+      <c r="E46" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F46" s="29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="14"/>
+      <c r="B47" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C47" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D47" s="28">
+        <v>15.13</v>
+      </c>
+      <c r="E47" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="14"/>
+      <c r="B48" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D43" s="32">
-        <v>11</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F43" s="33">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D44" s="32">
-        <v>52.19</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F44" s="33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D45" s="32">
-        <v>87.74</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F45" s="33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="26"/>
-      <c r="B46" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D46" s="32">
-        <v>15.13</v>
-      </c>
-      <c r="E46" s="18" t="s">
+      <c r="D48" s="28">
+        <v>43.63</v>
+      </c>
+      <c r="E48" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="F46" s="33">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="26"/>
-      <c r="B47" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D47" s="32">
-        <v>43.63</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="F47" s="33">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D48" s="32">
-        <v>14.59</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="F48" s="33">
-        <v>13</v>
+      <c r="F48" s="29">
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B49" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D49" s="28">
+        <v>14.59</v>
+      </c>
+      <c r="E49" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F49" s="29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D50" s="28">
+        <v>36.869999999999997</v>
+      </c>
+      <c r="E50" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="F50" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="14"/>
+      <c r="B51" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C51" s="16"/>
+      <c r="D51" s="28">
+        <v>24.14</v>
+      </c>
+      <c r="E51" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="14"/>
+      <c r="B52" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="D52" s="28">
+        <v>12.46</v>
+      </c>
+      <c r="E52" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="14"/>
+      <c r="B53" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D49" s="32">
-        <v>36.869999999999997</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F49" s="33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="26"/>
-      <c r="B50" s="12" t="s">
+      <c r="C53" s="16"/>
+      <c r="D53" s="28">
+        <v>60.84</v>
+      </c>
+      <c r="E53" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="F53" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="14"/>
+      <c r="B54" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="C50" s="28"/>
-      <c r="D50" s="32">
-        <v>24.14</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="F50" s="33">
+      <c r="C54" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D54" s="28">
+        <v>28.75</v>
+      </c>
+      <c r="E54" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54" s="29">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="14"/>
+      <c r="B55" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D55" s="28">
+        <v>58.82</v>
+      </c>
+      <c r="E55" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="14"/>
+      <c r="B56" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D56" s="28">
+        <v>23.490000000000002</v>
+      </c>
+      <c r="E56" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" s="29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="14"/>
+      <c r="B57" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D57" s="28">
+        <v>59.9</v>
+      </c>
+      <c r="E57" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" s="29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="14"/>
+      <c r="B58" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C58" s="16"/>
+      <c r="D58" s="28">
+        <v>8.36</v>
+      </c>
+      <c r="E58" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="26"/>
-      <c r="B51" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="C51" s="28"/>
-      <c r="D51" s="32">
-        <v>12.46</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="F51" s="33">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="14"/>
+      <c r="B59" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="C59" s="16"/>
+      <c r="D59" s="28">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="E59" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="26"/>
-      <c r="B52" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="C52" s="28"/>
-      <c r="D52" s="32">
-        <v>60.84</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F52" s="33">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="14"/>
+      <c r="B60" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="C60" s="16"/>
+      <c r="D60" s="28">
+        <v>39.57</v>
+      </c>
+      <c r="E60" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="29">
         <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="26"/>
-      <c r="B53" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D53" s="32">
-        <v>28.75</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F53" s="33">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="26"/>
-      <c r="B54" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D54" s="32">
-        <v>58.82</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F54" s="33">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="26"/>
-      <c r="B55" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D55" s="32">
-        <v>23.490000000000002</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="F55" s="33">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="26"/>
-      <c r="B56" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D56" s="32">
-        <v>59.9</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="F56" s="33">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="26"/>
-      <c r="B57" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C57" s="28"/>
-      <c r="D57" s="32">
-        <v>8.36</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="F57" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="26"/>
-      <c r="B58" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="C58" s="28"/>
-      <c r="D58" s="32">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="26"/>
-      <c r="B59" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="32">
-        <v>39.57</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F59" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D60" s="32">
-        <v>18.5</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F60" s="33">
-        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>202</v>
+        <v>330</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D61" s="32">
-        <v>20.990000000000002</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="F61" s="33">
+        <v>277</v>
+      </c>
+      <c r="D61" s="28">
+        <v>18.5</v>
+      </c>
+      <c r="E61" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="29">
         <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>203</v>
+        <v>329</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D62" s="32">
-        <v>48.1</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F62" s="33">
-        <v>14</v>
+        <v>277</v>
+      </c>
+      <c r="D62" s="28">
+        <v>20.990000000000002</v>
+      </c>
+      <c r="E62" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="F62" s="29">
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>204</v>
+        <v>328</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>200</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D63" s="32">
-        <v>51.81</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="F63" s="33">
-        <v>12</v>
+        <v>279</v>
+      </c>
+      <c r="D63" s="28">
+        <v>48.1</v>
+      </c>
+      <c r="E63" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="F63" s="29">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>205</v>
+        <v>329</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>201</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D64" s="32">
-        <v>65.8</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="F64" s="33">
-        <v>1</v>
+      <c r="D64" s="28">
+        <v>51.81</v>
+      </c>
+      <c r="E64" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="F64" s="29">
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>206</v>
+        <v>333</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>202</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D65" s="32">
+        <v>277</v>
+      </c>
+      <c r="D65" s="39">
+        <v>65.8</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F65" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D66" s="39">
         <v>129.94999999999999</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E66" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F66" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="5"/>
+      <c r="B67" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="D67" s="39">
+        <v>255.92000000000002</v>
+      </c>
+      <c r="E67" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F65" s="33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="5"/>
-      <c r="B66" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="D66" s="32">
-        <v>255.92000000000002</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="F66" s="33">
+      <c r="F67" s="40">
         <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C67" s="2">
-        <v>100</v>
-      </c>
-      <c r="D67" s="32">
-        <v>11.8</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="F67" s="33">
-        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D68" s="32">
-        <v>13.16</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="F68" s="33">
-        <v>5</v>
+        <v>311</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C68" s="2">
+        <v>100</v>
+      </c>
+      <c r="D68" s="39">
+        <v>11.8</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F68" s="40">
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>209</v>
+        <v>311</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D69" s="32">
+        <v>353</v>
+      </c>
+      <c r="D69" s="39">
         <v>13.36</v>
       </c>
-      <c r="E69" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="F69" s="33">
-        <v>3</v>
+      <c r="E69" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F69" s="40">
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>210</v>
+        <v>311</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>206</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D70" s="32">
+        <v>354</v>
+      </c>
+      <c r="D70" s="39">
         <v>13.36</v>
       </c>
-      <c r="E70" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F70" s="33">
-        <v>7</v>
+      <c r="E70" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F70" s="40">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>211</v>
+        <v>311</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>207</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D71" s="32">
-        <v>14.14</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F71" s="33">
-        <v>3</v>
+        <v>355</v>
+      </c>
+      <c r="D71" s="39">
+        <v>13.36</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F71" s="40">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>212</v>
+        <v>311</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>208</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D72" s="32">
-        <v>12.780000000000001</v>
-      </c>
-      <c r="E72" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="F72" s="33">
-        <v>2</v>
+        <v>356</v>
+      </c>
+      <c r="D72" s="39">
+        <v>14.14</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F72" s="40">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>213</v>
+        <v>311</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>209</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D73" s="32">
-        <v>13.200000000000001</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="F73" s="33">
-        <v>3</v>
+        <v>357</v>
+      </c>
+      <c r="D73" s="39">
+        <v>12.780000000000001</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F73" s="40">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>214</v>
+        <v>311</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>210</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D74" s="32">
+        <v>358</v>
+      </c>
+      <c r="D74" s="39">
+        <v>13.200000000000001</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F74" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D75" s="39">
         <v>14.35</v>
       </c>
-      <c r="E74" s="18" t="s">
+      <c r="E75" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F75" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="14"/>
+      <c r="B76" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="D76" s="39">
+        <v>31.02</v>
+      </c>
+      <c r="E76" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F74" s="33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="26"/>
-      <c r="B75" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="C75" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="D75" s="32">
-        <v>31.02</v>
-      </c>
-      <c r="E75" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="F75" s="33">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D76" s="32">
-        <v>24.88</v>
-      </c>
-      <c r="E76" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="F76" s="33">
-        <v>2</v>
+      <c r="F76" s="40">
+        <v>-2</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>217</v>
+        <v>314</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>213</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D77" s="32">
-        <v>28.64</v>
-      </c>
-      <c r="E77" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F77" s="33">
-        <v>8</v>
+        <v>360</v>
+      </c>
+      <c r="D77" s="39">
+        <v>24.88</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F77" s="40">
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>218</v>
+        <v>314</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>214</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D78" s="32">
-        <v>28.22</v>
-      </c>
-      <c r="E78" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="F78" s="33">
-        <v>5</v>
+        <v>361</v>
+      </c>
+      <c r="D78" s="39">
+        <v>28.64</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F78" s="40">
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>219</v>
+        <v>314</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>215</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D79" s="32">
-        <v>28.650000000000002</v>
-      </c>
-      <c r="E79" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F79" s="33">
-        <v>4</v>
+        <v>359</v>
+      </c>
+      <c r="D79" s="39">
+        <v>28.22</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F79" s="40">
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>220</v>
+        <v>314</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>216</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D80" s="32">
-        <v>20.61</v>
-      </c>
-      <c r="E80" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="F80" s="33">
-        <v>7</v>
+        <v>355</v>
+      </c>
+      <c r="D80" s="39">
+        <v>28.650000000000002</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F80" s="40">
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>221</v>
+        <v>314</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D81" s="32">
-        <v>28.25</v>
-      </c>
-      <c r="E81" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="F81" s="33">
-        <v>8</v>
+        <v>353</v>
+      </c>
+      <c r="D81" s="39">
+        <v>20.61</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F81" s="40">
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>222</v>
+        <v>314</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D82" s="32">
-        <v>25.92</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="F82" s="33">
-        <v>5</v>
+        <v>356</v>
+      </c>
+      <c r="D82" s="39">
+        <v>28.68</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F82" s="40">
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>223</v>
+        <v>314</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D83" s="32">
-        <v>27.87</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="F83" s="33">
-        <v>4</v>
+        <v>357</v>
+      </c>
+      <c r="D83" s="39">
+        <v>25.92</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F83" s="40">
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>224</v>
+        <v>314</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D84" s="32">
-        <v>28.64</v>
-      </c>
-      <c r="E84" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="F84" s="33">
-        <v>5</v>
+        <v>358</v>
+      </c>
+      <c r="D84" s="39">
+        <v>27.87</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F84" s="40">
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>225</v>
+        <v>314</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D85" s="32">
-        <v>19.7</v>
-      </c>
-      <c r="E85" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="F85" s="33">
-        <v>0</v>
+        <v>354</v>
+      </c>
+      <c r="D85" s="39">
+        <v>28.64</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F85" s="40">
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="C86" s="28"/>
-      <c r="D86" s="32">
-        <v>79.86</v>
-      </c>
-      <c r="E86" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F86" s="33">
-        <v>5</v>
+        <v>222</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D86" s="39">
+        <v>19.7</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F86" s="40">
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D87" s="32">
-        <v>111.09</v>
-      </c>
-      <c r="E87" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F87" s="33">
-        <v>1</v>
+        <v>314</v>
+      </c>
+      <c r="B87" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="C87" s="16"/>
+      <c r="D87" s="39">
+        <v>79.86</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F87" s="40">
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>316</v>
+        <v>312</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>224</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D88" s="32">
-        <v>79.92</v>
-      </c>
-      <c r="E88" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F88" s="33">
-        <v>2</v>
+        <v>359</v>
+      </c>
+      <c r="D88" s="39">
+        <v>111.09</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F88" s="40">
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>228</v>
+        <v>312</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>313</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D89" s="32">
-        <v>20.7</v>
-      </c>
-      <c r="E89" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="F89" s="33">
-        <v>6</v>
+        <v>353</v>
+      </c>
+      <c r="D89" s="39">
+        <v>79.92</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F89" s="40">
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>229</v>
+        <v>332</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D90" s="32">
-        <v>56</v>
-      </c>
-      <c r="E90" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="F90" s="33">
-        <v>1</v>
+        <v>282</v>
+      </c>
+      <c r="D90" s="39">
+        <v>20.7</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F90" s="40">
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>230</v>
+        <v>332</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>226</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D91" s="32">
-        <v>112</v>
-      </c>
-      <c r="E91" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="F91" s="33">
-        <v>2</v>
+        <v>277</v>
+      </c>
+      <c r="D91" s="39">
+        <v>56</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F91" s="40">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>231</v>
+        <v>332</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D92" s="32">
-        <v>64.17</v>
-      </c>
-      <c r="E92" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F92" s="33">
+        <v>287</v>
+      </c>
+      <c r="D92" s="39">
+        <v>112</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F92" s="40">
         <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>232</v>
+        <v>334</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D93" s="32">
-        <v>12.68</v>
-      </c>
-      <c r="E93" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="F93" s="33">
-        <v>2</v>
+        <v>277</v>
+      </c>
+      <c r="D93" s="39">
+        <v>65.12</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F93" s="40">
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>233</v>
+        <v>310</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>229</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D94" s="32">
-        <v>12.91</v>
-      </c>
-      <c r="E94" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="F94" s="33">
-        <v>8</v>
+        <v>277</v>
+      </c>
+      <c r="D94" s="39">
+        <v>12.68</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F94" s="40">
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>234</v>
+        <v>309</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>230</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D95" s="32">
-        <v>27.330000000000002</v>
-      </c>
-      <c r="E95" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F95" s="33">
-        <v>0</v>
+        <v>277</v>
+      </c>
+      <c r="D95" s="39">
+        <v>12.91</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F95" s="40">
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>235</v>
+        <v>310</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>231</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D96" s="32">
-        <v>33.5</v>
-      </c>
-      <c r="E96" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="F96" s="33">
-        <v>5</v>
+        <v>276</v>
+      </c>
+      <c r="D96" s="39">
+        <v>27.330000000000002</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F96" s="40">
+        <v>161</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>236</v>
+        <v>309</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>232</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D97" s="32">
-        <v>38.880000000000003</v>
-      </c>
-      <c r="E97" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="F97" s="33">
-        <v>3</v>
+        <v>276</v>
+      </c>
+      <c r="D97" s="39">
+        <v>33.5</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F97" s="40">
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>237</v>
+        <v>315</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>233</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D98" s="32">
-        <v>8.66</v>
-      </c>
-      <c r="E98" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="F98" s="33">
-        <v>3</v>
+        <v>277</v>
+      </c>
+      <c r="D98" s="39">
+        <v>38.880000000000003</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F98" s="40">
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B99" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D99" s="39">
+        <v>8.66</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F99" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D100" s="39">
+        <v>69.650000000000006</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F100" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="14"/>
+      <c r="B101" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="D101" s="39">
+        <v>24.650000000000002</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F101" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D102" s="39">
+        <v>47.19</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F102" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="14"/>
+      <c r="B103" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="D103" s="39">
+        <v>29.080000000000002</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F103" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D104" s="39">
+        <v>32.69</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F104" s="40">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="14"/>
+      <c r="B105" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D105" s="39">
+        <v>24.26</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F105" s="40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="14"/>
+      <c r="B106" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D106" s="39">
+        <v>23.1</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F106" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="14"/>
+      <c r="B107" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D99" s="32">
-        <v>69.650000000000006</v>
-      </c>
-      <c r="E99" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="F99" s="33">
+      <c r="D107" s="39">
+        <v>7.8</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F107" s="40">
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="26"/>
-      <c r="B100" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="D100" s="32">
-        <v>24.650000000000002</v>
-      </c>
-      <c r="E100" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F100" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D101" s="32">
-        <v>47.19</v>
-      </c>
-      <c r="E101" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F101" s="33">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="26"/>
-      <c r="B102" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="D102" s="32">
-        <v>29.080000000000002</v>
-      </c>
-      <c r="E102" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="F102" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D103" s="32">
-        <v>32.69</v>
-      </c>
-      <c r="E103" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="F103" s="33">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="26"/>
-      <c r="B104" s="9" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="14"/>
+      <c r="B108" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="D108" s="39">
+        <v>7.66</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F108" s="40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="14"/>
+      <c r="B109" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D109" s="39">
+        <v>17.16</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F109" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="14"/>
+      <c r="B110" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D104" s="32">
-        <v>24.26</v>
-      </c>
-      <c r="E104" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="F104" s="33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="26"/>
-      <c r="B105" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D105" s="32">
-        <v>23.1</v>
-      </c>
-      <c r="E105" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="F105" s="33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="26"/>
-      <c r="B106" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D106" s="32">
-        <v>7.8</v>
-      </c>
-      <c r="E106" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="F106" s="33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="26"/>
-      <c r="B107" s="11" t="s">
+      <c r="D110" s="39">
+        <v>16.830000000000002</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="F110" s="40">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="14"/>
+      <c r="B111" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="D107" s="32">
-        <v>7.51</v>
-      </c>
-      <c r="E107" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F107" s="33">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="26"/>
-      <c r="B108" s="9" t="s">
+      <c r="C111" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D111" s="39">
+        <v>8.6</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F111" s="40">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="14"/>
+      <c r="B112" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="D108" s="32">
-        <v>17.16</v>
-      </c>
-      <c r="E108" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="F108" s="33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="26"/>
-      <c r="B109" s="9" t="s">
+      <c r="C112" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D112" s="39">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="E112" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F112" s="40">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="14"/>
+      <c r="B113" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D109" s="32">
-        <v>16.5</v>
-      </c>
-      <c r="E109" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="F109" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="26"/>
-      <c r="B110" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D110" s="32">
-        <v>8.4499999999999993</v>
-      </c>
-      <c r="E110" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="F110" s="33">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="26"/>
-      <c r="B111" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D111" s="32">
-        <v>30.66</v>
-      </c>
-      <c r="E111" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F111" s="33">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="26"/>
-      <c r="B112" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D112" s="32">
-        <v>32.44</v>
-      </c>
-      <c r="E112" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="F112" s="33">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="26"/>
-      <c r="B113" s="9" t="s">
-        <v>252</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D113" s="32">
+      <c r="D113" s="39">
+        <v>33.090000000000003</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F113" s="40">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="14"/>
+      <c r="B114" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D114" s="39">
         <v>8.86</v>
       </c>
-      <c r="E113" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F113" s="33">
+      <c r="E114" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F114" s="40">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D114" s="32">
-        <v>19.02</v>
-      </c>
-      <c r="E114" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="F114" s="33">
-        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>254</v>
+        <v>338</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>250</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D115" s="32">
-        <v>51.44</v>
-      </c>
-      <c r="E115" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="D115" s="39">
+        <v>19.41</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F115" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D116" s="39">
+        <v>65.33</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F116" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="14"/>
+      <c r="B117" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D117" s="39">
+        <v>11.82</v>
+      </c>
+      <c r="E117" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F115" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="26"/>
-      <c r="B116" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D116" s="32">
-        <v>11.58</v>
-      </c>
-      <c r="E116" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="F116" s="33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D117" s="32">
-        <v>35.56</v>
-      </c>
-      <c r="E117" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="F117" s="33">
-        <v>5</v>
+      <c r="F117" s="40">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="B118" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D118" s="39">
+        <v>35.56</v>
+      </c>
+      <c r="E118" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F118" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D119" s="39">
+        <v>89.14</v>
+      </c>
+      <c r="E119" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F119" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="14"/>
+      <c r="B120" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D120" s="39">
+        <v>24.32</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F120" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="14"/>
+      <c r="B121" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D121" s="39">
+        <v>31.240000000000002</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F121" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="14"/>
+      <c r="B122" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C122" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D122" s="39">
+        <v>28.82</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F122" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="14"/>
+      <c r="B123" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D123" s="39">
+        <v>72.710000000000008</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F123" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="14"/>
+      <c r="B124" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D124" s="39">
+        <v>9.84</v>
+      </c>
+      <c r="E124" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F124" s="40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="14"/>
+      <c r="B125" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D118" s="32">
-        <v>89.14</v>
-      </c>
-      <c r="E118" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="F118" s="33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="26"/>
-      <c r="B119" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D119" s="32">
-        <v>24.32</v>
-      </c>
-      <c r="E119" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="F119" s="33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="26"/>
-      <c r="B120" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="C120" s="2" t="s">
+      <c r="D125" s="39">
+        <v>23.8</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F125" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="14"/>
+      <c r="B126" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D126" s="39">
+        <v>35.68</v>
+      </c>
+      <c r="E126" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F126" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="14"/>
+      <c r="B127" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D127" s="39">
+        <v>18.22</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F127" s="40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="14"/>
+      <c r="B128" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D120" s="32">
-        <v>31.240000000000002</v>
-      </c>
-      <c r="E120" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="F120" s="33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="26"/>
-      <c r="B121" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D121" s="32">
-        <v>28.82</v>
-      </c>
-      <c r="E121" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F121" s="33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="26"/>
-      <c r="B122" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D122" s="32">
-        <v>72.710000000000008</v>
-      </c>
-      <c r="E122" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="F122" s="33">
+      <c r="D128" s="39">
+        <v>18.150000000000002</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F128" s="40">
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="26"/>
-      <c r="B123" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="C123" s="2" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="14"/>
+      <c r="B129" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D123" s="32">
-        <v>9.64</v>
-      </c>
-      <c r="E123" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F123" s="33">
+      <c r="D129" s="39">
+        <v>15.63</v>
+      </c>
+      <c r="E129" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F129" s="40">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="14"/>
+      <c r="B130" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D130" s="39">
+        <v>29.5</v>
+      </c>
+      <c r="E130" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F130" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="14"/>
+      <c r="B131" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D131" s="39">
+        <v>49.51</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F131" s="40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="14"/>
+      <c r="B132" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D132" s="39">
+        <v>64</v>
+      </c>
+      <c r="E132" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F132" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="14"/>
+      <c r="B133" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="D133" s="39">
+        <v>18.37</v>
+      </c>
+      <c r="E133" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F133" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="26"/>
-      <c r="B124" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D124" s="32">
-        <v>23.8</v>
-      </c>
-      <c r="E124" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F124" s="33">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="14"/>
+      <c r="B134" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="D134" s="39">
+        <v>39.57</v>
+      </c>
+      <c r="E134" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F134" s="40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="14"/>
+      <c r="B135" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D135" s="39">
+        <v>44.78</v>
+      </c>
+      <c r="E135" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F135" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="14"/>
+      <c r="B136" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="D136" s="39">
+        <v>44.61</v>
+      </c>
+      <c r="E136" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F136" s="40">
         <v>3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="26"/>
-      <c r="B125" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D125" s="32">
-        <v>35.68</v>
-      </c>
-      <c r="E125" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F125" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="26"/>
-      <c r="B126" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D126" s="32">
-        <v>18.22</v>
-      </c>
-      <c r="E126" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="F126" s="33">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="26"/>
-      <c r="B127" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D127" s="32">
-        <v>18.150000000000002</v>
-      </c>
-      <c r="E127" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="F127" s="33">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="26"/>
-      <c r="B128" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D128" s="32">
-        <v>15.32</v>
-      </c>
-      <c r="E128" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F128" s="33">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="26"/>
-      <c r="B129" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D129" s="32">
-        <v>29.5</v>
-      </c>
-      <c r="E129" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F129" s="33">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="26"/>
-      <c r="B130" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D130" s="32">
-        <v>44</v>
-      </c>
-      <c r="E130" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="F130" s="33">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="26"/>
-      <c r="B131" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D131" s="32">
-        <v>64</v>
-      </c>
-      <c r="E131" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="F131" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="26"/>
-      <c r="B132" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="D132" s="32">
-        <v>18.37</v>
-      </c>
-      <c r="E132" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="F132" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="26"/>
-      <c r="B133" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="D133" s="32">
-        <v>39.57</v>
-      </c>
-      <c r="E133" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="F133" s="33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="26"/>
-      <c r="B134" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D134" s="32">
-        <v>44.78</v>
-      </c>
-      <c r="E134" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="F134" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="26"/>
-      <c r="B135" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="D135" s="32">
-        <v>43.74</v>
-      </c>
-      <c r="E135" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="F135" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B136" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D136" s="32">
-        <v>25.22</v>
-      </c>
-      <c r="E136" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="F136" s="33">
-        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>276</v>
+        <v>325</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>272</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D137" s="32">
-        <v>52.01</v>
-      </c>
-      <c r="E137" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="F137" s="33">
-        <v>2</v>
+        <v>285</v>
+      </c>
+      <c r="D137" s="39">
+        <v>25.22</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F137" s="40">
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="B138" s="9" t="s">
-        <v>277</v>
+        <v>325</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D138" s="32">
-        <v>24.32</v>
-      </c>
-      <c r="E138" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="F138" s="33">
-        <v>8</v>
+        <v>297</v>
+      </c>
+      <c r="D138" s="39">
+        <v>52.01</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F138" s="40">
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B139" s="25" t="s">
-        <v>305</v>
+        <v>337</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>274</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D139" s="5">
-        <v>23.4</v>
-      </c>
-      <c r="E139" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="F139" s="5">
-        <v>0</v>
+        <v>292</v>
+      </c>
+      <c r="D139" s="39">
+        <v>24.32</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F139" s="40">
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B140" s="25" t="s">
-        <v>306</v>
+        <v>305</v>
+      </c>
+      <c r="B140" s="38" t="s">
+        <v>302</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D140" s="5">
-        <v>14.37</v>
-      </c>
-      <c r="E140" s="24" t="s">
-        <v>304</v>
+        <v>23.4</v>
+      </c>
+      <c r="E140" s="36" t="s">
+        <v>363</v>
       </c>
       <c r="F140" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>351</v>
+        <v>304</v>
+      </c>
+      <c r="B141" s="38" t="s">
+        <v>303</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="D141" s="5">
-        <v>17.16</v>
-      </c>
-      <c r="E141" s="24" t="s">
-        <v>346</v>
+        <v>14.37</v>
+      </c>
+      <c r="E141" s="36" t="s">
+        <v>301</v>
       </c>
       <c r="F141" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="B142" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
+      </c>
+      <c r="B142" s="38" t="s">
+        <v>348</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D142" s="5">
-        <v>29.35</v>
-      </c>
-      <c r="E142" s="24" t="s">
-        <v>348</v>
+        <v>17.16</v>
+      </c>
+      <c r="E142" s="11" t="s">
+        <v>343</v>
       </c>
       <c r="F142" s="5">
         <v>6</v>
@@ -4363,1334 +4382,1354 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="B143" s="5" t="s">
         <v>350</v>
       </c>
+      <c r="B143" s="38" t="s">
+        <v>344</v>
+      </c>
       <c r="C143" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D143" s="5">
+        <v>29.35</v>
+      </c>
+      <c r="E143" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="F143" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D144" s="5">
         <v>6.01</v>
       </c>
-      <c r="E143" s="24" t="s">
-        <v>349</v>
-      </c>
-      <c r="F143" s="5">
+      <c r="E144" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F144" s="5">
         <v>20</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="5"/>
-      <c r="B144" s="5"/>
-      <c r="D144" s="5"/>
-      <c r="E144" s="13"/>
-      <c r="F144" s="5"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="D145" s="5"/>
-      <c r="E145" s="13"/>
+      <c r="E145" s="11"/>
       <c r="F145" s="5"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="D146" s="5"/>
-      <c r="E146" s="13"/>
+      <c r="E146" s="11"/>
       <c r="F146" s="5"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="D147" s="5"/>
-      <c r="E147" s="13"/>
+      <c r="E147" s="11"/>
       <c r="F147" s="5"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="D148" s="5"/>
-      <c r="E148" s="13"/>
+      <c r="E148" s="11"/>
       <c r="F148" s="5"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="D149" s="5"/>
-      <c r="E149" s="13"/>
+      <c r="E149" s="11"/>
       <c r="F149" s="5"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="D150" s="5"/>
-      <c r="E150" s="13"/>
+      <c r="E150" s="11"/>
       <c r="F150" s="5"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="D151" s="5"/>
-      <c r="E151" s="13"/>
+      <c r="E151" s="11"/>
       <c r="F151" s="5"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="D152" s="5"/>
-      <c r="E152" s="13"/>
+      <c r="E152" s="11"/>
       <c r="F152" s="5"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="D153" s="5"/>
-      <c r="E153" s="13"/>
+      <c r="E153" s="11"/>
       <c r="F153" s="5"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="D154" s="5"/>
-      <c r="E154" s="13"/>
+      <c r="E154" s="11"/>
       <c r="F154" s="5"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="D155" s="5"/>
-      <c r="E155" s="13"/>
+      <c r="E155" s="11"/>
       <c r="F155" s="5"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="D156" s="5"/>
-      <c r="E156" s="13"/>
+      <c r="E156" s="11"/>
       <c r="F156" s="5"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="D157" s="5"/>
-      <c r="E157" s="13"/>
+      <c r="E157" s="11"/>
       <c r="F157" s="5"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="D158" s="5"/>
-      <c r="E158" s="13"/>
+      <c r="E158" s="11"/>
       <c r="F158" s="5"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="D159" s="5"/>
-      <c r="E159" s="13"/>
+      <c r="E159" s="11"/>
       <c r="F159" s="5"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="D160" s="5"/>
-      <c r="E160" s="13"/>
+      <c r="E160" s="11"/>
       <c r="F160" s="5"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="D161" s="5"/>
-      <c r="E161" s="13"/>
+      <c r="E161" s="11"/>
       <c r="F161" s="5"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="D162" s="5"/>
-      <c r="E162" s="13"/>
+      <c r="E162" s="11"/>
       <c r="F162" s="5"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="D163" s="5"/>
-      <c r="E163" s="13"/>
+      <c r="E163" s="11"/>
       <c r="F163" s="5"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="D164" s="5"/>
-      <c r="E164" s="13"/>
+      <c r="E164" s="11"/>
       <c r="F164" s="5"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="D165" s="5"/>
-      <c r="E165" s="13"/>
+      <c r="E165" s="11"/>
       <c r="F165" s="5"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="D166" s="5"/>
-      <c r="E166" s="13"/>
+      <c r="E166" s="11"/>
       <c r="F166" s="5"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="D167" s="5"/>
-      <c r="E167" s="13"/>
+      <c r="E167" s="11"/>
       <c r="F167" s="5"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="D168" s="5"/>
-      <c r="E168" s="13"/>
+      <c r="E168" s="11"/>
       <c r="F168" s="5"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="D169" s="5"/>
-      <c r="E169" s="13"/>
+      <c r="E169" s="11"/>
       <c r="F169" s="5"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="D170" s="5"/>
-      <c r="E170" s="13"/>
+      <c r="E170" s="11"/>
       <c r="F170" s="5"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="D171" s="5"/>
-      <c r="E171" s="13"/>
+      <c r="E171" s="11"/>
       <c r="F171" s="5"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="D172" s="5"/>
-      <c r="E172" s="13"/>
+      <c r="E172" s="11"/>
       <c r="F172" s="5"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="D173" s="5"/>
-      <c r="E173" s="13"/>
+      <c r="E173" s="11"/>
       <c r="F173" s="5"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="D174" s="5"/>
-      <c r="E174" s="13"/>
+      <c r="E174" s="11"/>
       <c r="F174" s="5"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="D175" s="5"/>
-      <c r="E175" s="13"/>
+      <c r="E175" s="11"/>
       <c r="F175" s="5"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="D176" s="5"/>
-      <c r="E176" s="13"/>
+      <c r="E176" s="11"/>
       <c r="F176" s="5"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="D177" s="5"/>
-      <c r="E177" s="13"/>
+      <c r="E177" s="11"/>
       <c r="F177" s="5"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="D178" s="5"/>
-      <c r="E178" s="13"/>
+      <c r="E178" s="11"/>
       <c r="F178" s="5"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="D179" s="5"/>
-      <c r="E179" s="13"/>
+      <c r="E179" s="11"/>
       <c r="F179" s="5"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="D180" s="5"/>
-      <c r="E180" s="13"/>
+      <c r="E180" s="11"/>
       <c r="F180" s="5"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="D181" s="5"/>
-      <c r="E181" s="13"/>
+      <c r="E181" s="11"/>
       <c r="F181" s="5"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="D182" s="5"/>
-      <c r="E182" s="13"/>
+      <c r="E182" s="11"/>
       <c r="F182" s="5"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="D183" s="5"/>
-      <c r="E183" s="13"/>
+      <c r="E183" s="11"/>
       <c r="F183" s="5"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="D184" s="5"/>
-      <c r="E184" s="13"/>
+      <c r="E184" s="11"/>
       <c r="F184" s="5"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="D185" s="5"/>
-      <c r="E185" s="13"/>
+      <c r="E185" s="11"/>
       <c r="F185" s="5"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="D186" s="5"/>
-      <c r="E186" s="13"/>
+      <c r="E186" s="11"/>
       <c r="F186" s="5"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="D187" s="5"/>
-      <c r="E187" s="13"/>
+      <c r="E187" s="11"/>
       <c r="F187" s="5"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="D188" s="5"/>
-      <c r="E188" s="13"/>
+      <c r="E188" s="11"/>
       <c r="F188" s="5"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="D189" s="5"/>
-      <c r="E189" s="13"/>
+      <c r="E189" s="11"/>
       <c r="F189" s="5"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="D190" s="5"/>
-      <c r="E190" s="13"/>
+      <c r="E190" s="11"/>
       <c r="F190" s="5"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="D191" s="5"/>
-      <c r="E191" s="13"/>
+      <c r="E191" s="11"/>
       <c r="F191" s="5"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="D192" s="5"/>
-      <c r="E192" s="13"/>
+      <c r="E192" s="11"/>
       <c r="F192" s="5"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="D193" s="5"/>
-      <c r="E193" s="13"/>
+      <c r="E193" s="11"/>
       <c r="F193" s="5"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="D194" s="5"/>
-      <c r="E194" s="13"/>
+      <c r="E194" s="11"/>
       <c r="F194" s="5"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="D195" s="5"/>
-      <c r="E195" s="13"/>
+      <c r="E195" s="11"/>
       <c r="F195" s="5"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="D196" s="5"/>
-      <c r="E196" s="13"/>
+      <c r="E196" s="11"/>
       <c r="F196" s="5"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="D197" s="5"/>
-      <c r="E197" s="13"/>
+      <c r="E197" s="11"/>
       <c r="F197" s="5"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="D198" s="5"/>
-      <c r="E198" s="13"/>
+      <c r="E198" s="11"/>
       <c r="F198" s="5"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="D199" s="5"/>
-      <c r="E199" s="13"/>
+      <c r="E199" s="11"/>
       <c r="F199" s="5"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="D200" s="5"/>
-      <c r="E200" s="13"/>
+      <c r="E200" s="11"/>
       <c r="F200" s="5"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="D201" s="5"/>
-      <c r="E201" s="13"/>
+      <c r="E201" s="11"/>
       <c r="F201" s="5"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="D202" s="5"/>
-      <c r="E202" s="13"/>
+      <c r="E202" s="11"/>
       <c r="F202" s="5"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="D203" s="5"/>
-      <c r="E203" s="13"/>
+      <c r="E203" s="11"/>
       <c r="F203" s="5"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="D204" s="5"/>
-      <c r="E204" s="13"/>
+      <c r="E204" s="11"/>
       <c r="F204" s="5"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="D205" s="5"/>
-      <c r="E205" s="13"/>
+      <c r="E205" s="11"/>
       <c r="F205" s="5"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="D206" s="5"/>
-      <c r="E206" s="13"/>
+      <c r="E206" s="11"/>
       <c r="F206" s="5"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="D207" s="5"/>
-      <c r="E207" s="13"/>
+      <c r="E207" s="11"/>
       <c r="F207" s="5"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="D208" s="5"/>
-      <c r="E208" s="13"/>
+      <c r="E208" s="11"/>
       <c r="F208" s="5"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="D209" s="5"/>
-      <c r="E209" s="13"/>
+      <c r="E209" s="11"/>
       <c r="F209" s="5"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="D210" s="5"/>
-      <c r="E210" s="13"/>
+      <c r="E210" s="11"/>
       <c r="F210" s="5"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="D211" s="5"/>
-      <c r="E211" s="13"/>
+      <c r="E211" s="11"/>
       <c r="F211" s="5"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="D212" s="5"/>
-      <c r="E212" s="13"/>
+      <c r="E212" s="11"/>
       <c r="F212" s="5"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="D213" s="5"/>
-      <c r="E213" s="13"/>
+      <c r="E213" s="11"/>
       <c r="F213" s="5"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="D214" s="5"/>
-      <c r="E214" s="13"/>
+      <c r="E214" s="11"/>
       <c r="F214" s="5"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="D215" s="5"/>
-      <c r="E215" s="13"/>
+      <c r="E215" s="11"/>
       <c r="F215" s="5"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="D216" s="5"/>
-      <c r="E216" s="13"/>
+      <c r="E216" s="11"/>
       <c r="F216" s="5"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="D217" s="5"/>
-      <c r="E217" s="13"/>
+      <c r="E217" s="11"/>
       <c r="F217" s="5"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="D218" s="5"/>
-      <c r="E218" s="13"/>
+      <c r="E218" s="11"/>
       <c r="F218" s="5"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="D219" s="5"/>
-      <c r="E219" s="13"/>
+      <c r="E219" s="11"/>
       <c r="F219" s="5"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="D220" s="5"/>
-      <c r="E220" s="13"/>
+      <c r="E220" s="11"/>
       <c r="F220" s="5"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="D221" s="5"/>
-      <c r="E221" s="13"/>
+      <c r="E221" s="11"/>
       <c r="F221" s="5"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="D222" s="5"/>
-      <c r="E222" s="13"/>
+      <c r="E222" s="11"/>
       <c r="F222" s="5"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="D223" s="5"/>
-      <c r="E223" s="13"/>
+      <c r="E223" s="11"/>
       <c r="F223" s="5"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="D224" s="5"/>
-      <c r="E224" s="13"/>
+      <c r="E224" s="11"/>
       <c r="F224" s="5"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="D225" s="5"/>
-      <c r="E225" s="13"/>
+      <c r="E225" s="11"/>
       <c r="F225" s="5"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="D226" s="5"/>
-      <c r="E226" s="13"/>
+      <c r="E226" s="11"/>
       <c r="F226" s="5"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="D227" s="5"/>
-      <c r="E227" s="13"/>
+      <c r="E227" s="11"/>
       <c r="F227" s="5"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="D228" s="5"/>
-      <c r="E228" s="13"/>
+      <c r="E228" s="11"/>
       <c r="F228" s="5"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="D229" s="5"/>
-      <c r="E229" s="13"/>
+      <c r="E229" s="11"/>
       <c r="F229" s="5"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="D230" s="5"/>
-      <c r="E230" s="13"/>
+      <c r="E230" s="11"/>
       <c r="F230" s="5"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="D231" s="5"/>
-      <c r="E231" s="13"/>
+      <c r="E231" s="11"/>
       <c r="F231" s="5"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="D232" s="5"/>
-      <c r="E232" s="13"/>
+      <c r="E232" s="11"/>
       <c r="F232" s="5"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="D233" s="5"/>
-      <c r="E233" s="13"/>
+      <c r="E233" s="11"/>
       <c r="F233" s="5"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="D234" s="5"/>
-      <c r="E234" s="13"/>
+      <c r="E234" s="11"/>
       <c r="F234" s="5"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="D235" s="5"/>
-      <c r="E235" s="13"/>
+      <c r="E235" s="11"/>
       <c r="F235" s="5"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="D236" s="5"/>
-      <c r="E236" s="13"/>
+      <c r="E236" s="11"/>
       <c r="F236" s="5"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="D237" s="5"/>
-      <c r="E237" s="13"/>
+      <c r="E237" s="11"/>
       <c r="F237" s="5"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="D238" s="5"/>
-      <c r="E238" s="13"/>
+      <c r="E238" s="11"/>
       <c r="F238" s="5"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="D239" s="5"/>
-      <c r="E239" s="13"/>
+      <c r="E239" s="11"/>
       <c r="F239" s="5"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="D240" s="5"/>
-      <c r="E240" s="13"/>
+      <c r="E240" s="11"/>
       <c r="F240" s="5"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="D241" s="5"/>
-      <c r="E241" s="13"/>
+      <c r="E241" s="11"/>
       <c r="F241" s="5"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="D242" s="5"/>
-      <c r="E242" s="13"/>
+      <c r="E242" s="11"/>
       <c r="F242" s="5"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="D243" s="5"/>
-      <c r="E243" s="13"/>
+      <c r="E243" s="11"/>
       <c r="F243" s="5"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="D244" s="5"/>
-      <c r="E244" s="13"/>
+      <c r="E244" s="11"/>
       <c r="F244" s="5"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="D245" s="5"/>
-      <c r="E245" s="13"/>
+      <c r="E245" s="11"/>
       <c r="F245" s="5"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="D246" s="5"/>
-      <c r="E246" s="13"/>
+      <c r="E246" s="11"/>
       <c r="F246" s="5"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="D247" s="5"/>
-      <c r="E247" s="13"/>
+      <c r="E247" s="11"/>
       <c r="F247" s="5"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="D248" s="5"/>
-      <c r="E248" s="13"/>
+      <c r="E248" s="11"/>
       <c r="F248" s="5"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="D249" s="5"/>
-      <c r="E249" s="13"/>
+      <c r="E249" s="11"/>
       <c r="F249" s="5"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="D250" s="5"/>
-      <c r="E250" s="13"/>
+      <c r="E250" s="11"/>
       <c r="F250" s="5"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="D251" s="5"/>
-      <c r="E251" s="13"/>
+      <c r="E251" s="11"/>
       <c r="F251" s="5"/>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="D252" s="5"/>
-      <c r="E252" s="13"/>
+      <c r="E252" s="11"/>
       <c r="F252" s="5"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="D253" s="5"/>
-      <c r="E253" s="13"/>
+      <c r="E253" s="11"/>
       <c r="F253" s="5"/>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="D254" s="5"/>
-      <c r="E254" s="13"/>
+      <c r="E254" s="11"/>
       <c r="F254" s="5"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="D255" s="5"/>
-      <c r="E255" s="13"/>
+      <c r="E255" s="11"/>
       <c r="F255" s="5"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="D256" s="5"/>
-      <c r="E256" s="13"/>
+      <c r="E256" s="11"/>
       <c r="F256" s="5"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="D257" s="5"/>
-      <c r="E257" s="13"/>
+      <c r="E257" s="11"/>
       <c r="F257" s="5"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="D258" s="5"/>
-      <c r="E258" s="13"/>
+      <c r="E258" s="11"/>
       <c r="F258" s="5"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="D259" s="5"/>
-      <c r="E259" s="13"/>
+      <c r="E259" s="11"/>
       <c r="F259" s="5"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="D260" s="5"/>
-      <c r="E260" s="13"/>
+      <c r="E260" s="11"/>
       <c r="F260" s="5"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="D261" s="5"/>
-      <c r="E261" s="13"/>
+      <c r="E261" s="11"/>
       <c r="F261" s="5"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="D262" s="5"/>
-      <c r="E262" s="13"/>
+      <c r="E262" s="11"/>
       <c r="F262" s="5"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="D263" s="5"/>
-      <c r="E263" s="13"/>
+      <c r="E263" s="11"/>
       <c r="F263" s="5"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="D264" s="5"/>
-      <c r="E264" s="13"/>
+      <c r="E264" s="11"/>
       <c r="F264" s="5"/>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="D265" s="5"/>
-      <c r="E265" s="13"/>
+      <c r="E265" s="11"/>
       <c r="F265" s="5"/>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="D266" s="5"/>
-      <c r="E266" s="13"/>
+      <c r="E266" s="11"/>
       <c r="F266" s="5"/>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="D267" s="5"/>
-      <c r="E267" s="13"/>
+      <c r="E267" s="11"/>
       <c r="F267" s="5"/>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="D268" s="5"/>
-      <c r="E268" s="13"/>
+      <c r="E268" s="11"/>
       <c r="F268" s="5"/>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="D269" s="5"/>
-      <c r="E269" s="13"/>
+      <c r="E269" s="11"/>
       <c r="F269" s="5"/>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="D270" s="5"/>
-      <c r="E270" s="13"/>
+      <c r="E270" s="11"/>
       <c r="F270" s="5"/>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="D271" s="5"/>
-      <c r="E271" s="13"/>
+      <c r="E271" s="11"/>
       <c r="F271" s="5"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="D272" s="5"/>
-      <c r="E272" s="13"/>
+      <c r="E272" s="11"/>
       <c r="F272" s="5"/>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="D273" s="5"/>
-      <c r="E273" s="13"/>
+      <c r="E273" s="11"/>
       <c r="F273" s="5"/>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="D274" s="5"/>
-      <c r="E274" s="13"/>
+      <c r="E274" s="11"/>
       <c r="F274" s="5"/>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="D275" s="5"/>
-      <c r="E275" s="13"/>
+      <c r="E275" s="11"/>
       <c r="F275" s="5"/>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="D276" s="5"/>
-      <c r="E276" s="13"/>
+      <c r="E276" s="11"/>
       <c r="F276" s="5"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="D277" s="5"/>
-      <c r="E277" s="13"/>
+      <c r="E277" s="11"/>
       <c r="F277" s="5"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="D278" s="5"/>
-      <c r="E278" s="13"/>
+      <c r="E278" s="11"/>
       <c r="F278" s="5"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="D279" s="5"/>
-      <c r="E279" s="13"/>
+      <c r="E279" s="11"/>
       <c r="F279" s="5"/>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="D280" s="5"/>
-      <c r="E280" s="13"/>
+      <c r="E280" s="11"/>
       <c r="F280" s="5"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="D281" s="5"/>
-      <c r="E281" s="13"/>
+      <c r="E281" s="11"/>
       <c r="F281" s="5"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="D282" s="5"/>
-      <c r="E282" s="13"/>
+      <c r="E282" s="11"/>
       <c r="F282" s="5"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="D283" s="5"/>
-      <c r="E283" s="13"/>
+      <c r="E283" s="11"/>
       <c r="F283" s="5"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="D284" s="5"/>
-      <c r="E284" s="13"/>
+      <c r="E284" s="11"/>
       <c r="F284" s="5"/>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="D285" s="5"/>
-      <c r="E285" s="13"/>
+      <c r="E285" s="11"/>
       <c r="F285" s="5"/>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="D286" s="5"/>
-      <c r="E286" s="13"/>
+      <c r="E286" s="11"/>
       <c r="F286" s="5"/>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="D287" s="5"/>
-      <c r="E287" s="13"/>
+      <c r="E287" s="11"/>
       <c r="F287" s="5"/>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="D288" s="5"/>
-      <c r="E288" s="13"/>
+      <c r="E288" s="11"/>
       <c r="F288" s="5"/>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="D289" s="5"/>
-      <c r="E289" s="13"/>
+      <c r="E289" s="11"/>
       <c r="F289" s="5"/>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="D290" s="5"/>
-      <c r="E290" s="13"/>
+      <c r="E290" s="11"/>
       <c r="F290" s="5"/>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="D291" s="5"/>
-      <c r="E291" s="13"/>
+      <c r="E291" s="11"/>
       <c r="F291" s="5"/>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="D292" s="5"/>
-      <c r="E292" s="13"/>
+      <c r="E292" s="11"/>
       <c r="F292" s="5"/>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="D293" s="5"/>
-      <c r="E293" s="13"/>
+      <c r="E293" s="11"/>
       <c r="F293" s="5"/>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="D294" s="5"/>
-      <c r="E294" s="13"/>
+      <c r="E294" s="11"/>
       <c r="F294" s="5"/>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="D295" s="5"/>
-      <c r="E295" s="13"/>
+      <c r="E295" s="11"/>
       <c r="F295" s="5"/>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="D296" s="5"/>
-      <c r="E296" s="13"/>
+      <c r="E296" s="11"/>
       <c r="F296" s="5"/>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="D297" s="5"/>
-      <c r="E297" s="13"/>
+      <c r="E297" s="11"/>
       <c r="F297" s="5"/>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="D298" s="5"/>
-      <c r="E298" s="13"/>
+      <c r="E298" s="11"/>
       <c r="F298" s="5"/>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="D299" s="5"/>
-      <c r="E299" s="13"/>
+      <c r="E299" s="11"/>
       <c r="F299" s="5"/>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="D300" s="5"/>
-      <c r="E300" s="13"/>
+      <c r="E300" s="11"/>
       <c r="F300" s="5"/>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="D301" s="5"/>
-      <c r="E301" s="13"/>
+      <c r="E301" s="11"/>
       <c r="F301" s="5"/>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="D302" s="5"/>
-      <c r="E302" s="13"/>
+      <c r="E302" s="11"/>
       <c r="F302" s="5"/>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="D303" s="5"/>
-      <c r="E303" s="13"/>
+      <c r="E303" s="11"/>
       <c r="F303" s="5"/>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="D304" s="5"/>
-      <c r="E304" s="13"/>
+      <c r="E304" s="11"/>
       <c r="F304" s="5"/>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="D305" s="5"/>
-      <c r="E305" s="13"/>
+      <c r="E305" s="11"/>
       <c r="F305" s="5"/>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="D306" s="5"/>
-      <c r="E306" s="13"/>
+      <c r="E306" s="11"/>
       <c r="F306" s="5"/>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="D307" s="5"/>
-      <c r="E307" s="13"/>
+      <c r="E307" s="11"/>
       <c r="F307" s="5"/>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="D308" s="5"/>
-      <c r="E308" s="13"/>
+      <c r="E308" s="11"/>
       <c r="F308" s="5"/>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="D309" s="5"/>
-      <c r="E309" s="13"/>
+      <c r="E309" s="11"/>
       <c r="F309" s="5"/>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="D310" s="5"/>
-      <c r="E310" s="13"/>
+      <c r="E310" s="11"/>
       <c r="F310" s="5"/>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="D311" s="5"/>
-      <c r="E311" s="13"/>
+      <c r="E311" s="11"/>
       <c r="F311" s="5"/>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="D312" s="5"/>
-      <c r="E312" s="13"/>
+      <c r="E312" s="11"/>
       <c r="F312" s="5"/>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="D313" s="5"/>
-      <c r="E313" s="13"/>
+      <c r="E313" s="11"/>
       <c r="F313" s="5"/>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="D314" s="5"/>
-      <c r="E314" s="13"/>
+      <c r="E314" s="11"/>
       <c r="F314" s="5"/>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="D315" s="5"/>
-      <c r="E315" s="13"/>
+      <c r="E315" s="11"/>
       <c r="F315" s="5"/>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="D316" s="5"/>
-      <c r="E316" s="13"/>
+      <c r="E316" s="11"/>
       <c r="F316" s="5"/>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="D317" s="5"/>
-      <c r="E317" s="13"/>
+      <c r="E317" s="11"/>
       <c r="F317" s="5"/>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="D318" s="5"/>
-      <c r="E318" s="13"/>
+      <c r="E318" s="11"/>
       <c r="F318" s="5"/>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="D319" s="5"/>
-      <c r="E319" s="13"/>
+      <c r="E319" s="11"/>
       <c r="F319" s="5"/>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="D320" s="5"/>
-      <c r="E320" s="13"/>
+      <c r="E320" s="11"/>
       <c r="F320" s="5"/>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="D321" s="5"/>
-      <c r="E321" s="13"/>
+      <c r="E321" s="11"/>
       <c r="F321" s="5"/>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="D322" s="5"/>
-      <c r="E322" s="13"/>
+      <c r="E322" s="11"/>
       <c r="F322" s="5"/>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="D323" s="5"/>
-      <c r="E323" s="13"/>
+      <c r="E323" s="11"/>
       <c r="F323" s="5"/>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="D324" s="5"/>
-      <c r="E324" s="13"/>
+      <c r="E324" s="11"/>
       <c r="F324" s="5"/>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="D325" s="5"/>
-      <c r="E325" s="13"/>
+      <c r="E325" s="11"/>
       <c r="F325" s="5"/>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="D326" s="5"/>
-      <c r="E326" s="13"/>
+      <c r="E326" s="11"/>
       <c r="F326" s="5"/>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="D327" s="5"/>
-      <c r="E327" s="13"/>
+      <c r="E327" s="11"/>
       <c r="F327" s="5"/>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="D328" s="5"/>
-      <c r="E328" s="13"/>
+      <c r="E328" s="11"/>
       <c r="F328" s="5"/>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="D329" s="5"/>
-      <c r="E329" s="13"/>
+      <c r="E329" s="11"/>
       <c r="F329" s="5"/>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A330" s="2"/>
+      <c r="A330" s="5"/>
+      <c r="B330" s="5"/>
+      <c r="D330" s="5"/>
+      <c r="E330" s="11"/>
+      <c r="F330" s="5"/>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="2"/>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="2"/>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A333" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\produits-cimentaires\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA6140C-90AC-4181-84BE-CDF127532B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D3B115-FBC9-4C12-8809-9EA768ED2B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1265,7 +1265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1319,35 +1319,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1376,6 +1348,45 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1761,13 +1772,13 @@
         <v>276</v>
       </c>
       <c r="D2" s="3">
-        <v>28.48</v>
+        <v>29.97</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1783,7 +1794,7 @@
       <c r="D3" s="3">
         <v>52.83</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="26" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="5">
@@ -1803,7 +1814,7 @@
       <c r="D4" s="3">
         <v>74.100000000000009</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="26" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5">
@@ -1820,14 +1831,14 @@
       <c r="C5" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D5" s="19">
-        <v>31</v>
-      </c>
-      <c r="E5" s="35" t="s">
+      <c r="D5" s="30">
+        <v>29.900000000000002</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="20">
-        <v>9</v>
+      <c r="F5" s="31">
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1840,13 +1851,13 @@
       <c r="C6" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="30">
         <v>41.71</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="31">
         <v>9</v>
       </c>
     </row>
@@ -1860,13 +1871,13 @@
       <c r="C7" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="30">
         <v>74.62</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="31">
         <v>6</v>
       </c>
     </row>
@@ -1880,43 +1891,43 @@
       <c r="C8" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="32">
         <v>7.76</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="22">
-        <v>638</v>
+      <c r="F8" s="33">
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="14"/>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="32">
         <v>8.69</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="14"/>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="32">
         <v>11.370000000000001</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="33">
         <v>0</v>
       </c>
     </row>
@@ -1930,28 +1941,28 @@
       <c r="C11" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="32">
         <v>11.34</v>
       </c>
-      <c r="E11" s="34" t="s">
+      <c r="E11" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="22">
-        <v>33</v>
+      <c r="F11" s="33">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="14"/>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="32">
         <v>1.8</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="33">
         <v>0</v>
       </c>
     </row>
@@ -1965,13 +1976,13 @@
       <c r="C13" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="32">
         <v>7.95</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="33">
         <v>-5</v>
       </c>
     </row>
@@ -1985,13 +1996,13 @@
       <c r="C14" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="32">
         <v>15.950000000000001</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="33">
         <v>3</v>
       </c>
     </row>
@@ -2005,14 +2016,14 @@
       <c r="C15" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="32">
         <v>12.4</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="22">
-        <v>7</v>
+      <c r="F15" s="33">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2025,14 +2036,14 @@
       <c r="C16" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="21">
-        <v>10.620000000000001</v>
-      </c>
-      <c r="E16" s="34" t="s">
+      <c r="D16" s="32">
+        <v>11.6</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="22">
-        <v>12</v>
+      <c r="F16" s="33">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -2045,88 +2056,88 @@
       <c r="C17" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="32">
         <v>45.34</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="14"/>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="32">
         <v>7.71</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="14"/>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="32">
         <v>25.18</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="14"/>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="32">
         <v>9.84</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="14"/>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="32">
         <v>11.43</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="14"/>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="32">
         <v>13.55</v>
       </c>
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2135,13 +2146,13 @@
       <c r="B23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="32">
         <v>8.91</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="E23" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2155,13 +2166,13 @@
       <c r="C24" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="32">
         <v>12.870000000000001</v>
       </c>
-      <c r="E24" s="34" t="s">
+      <c r="E24" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="33">
         <v>-89</v>
       </c>
     </row>
@@ -2175,13 +2186,13 @@
       <c r="C25" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="32">
         <v>9.24</v>
       </c>
-      <c r="E25" s="34" t="s">
+      <c r="E25" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="33">
         <v>123</v>
       </c>
     </row>
@@ -2195,43 +2206,43 @@
       <c r="C26" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="32">
         <v>12.870000000000001</v>
       </c>
-      <c r="E26" s="34" t="s">
+      <c r="E26" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="22">
-        <v>72</v>
+      <c r="F26" s="33">
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="14"/>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="32">
         <v>10.370000000000001</v>
       </c>
-      <c r="E27" s="34" t="s">
+      <c r="E27" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="14"/>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="32">
         <v>10.67</v>
       </c>
-      <c r="E28" s="34" t="s">
+      <c r="E28" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2240,28 +2251,28 @@
       <c r="B29" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D29" s="32">
         <v>8.91</v>
       </c>
-      <c r="E29" s="34" t="s">
+      <c r="E29" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="14"/>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="32">
         <v>19.52</v>
       </c>
-      <c r="E30" s="34" t="s">
+      <c r="E30" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2275,28 +2286,28 @@
       <c r="C31" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="32">
         <v>23.28</v>
       </c>
-      <c r="E31" s="34" t="s">
+      <c r="E31" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="22">
-        <v>93</v>
+      <c r="F31" s="33">
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32" s="32">
         <v>31.470000000000002</v>
       </c>
-      <c r="E32" s="34" t="s">
+      <c r="E32" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2310,160 +2321,160 @@
       <c r="C33" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D33" s="21">
+      <c r="D33" s="32">
         <v>21.05</v>
       </c>
-      <c r="E33" s="34" t="s">
+      <c r="E33" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="22">
-        <v>88</v>
+      <c r="F33" s="33">
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="34">
         <v>5.51</v>
       </c>
-      <c r="E34" s="33" t="s">
+      <c r="E34" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="F34" s="27">
-        <v>13</v>
-      </c>
-      <c r="G34" s="24"/>
+      <c r="F34" s="35">
+        <v>9</v>
+      </c>
+      <c r="G34" s="19"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="29"/>
+      <c r="B35" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="D35" s="37">
+        <v>9</v>
+      </c>
+      <c r="E35" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="39">
+        <v>-5</v>
+      </c>
+      <c r="G35" s="19"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="B35" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D35" s="26">
-        <v>9</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="27">
-        <v>0</v>
-      </c>
-      <c r="G35" s="24"/>
-    </row>
-    <row r="36" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="17"/>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="19" t="s">
         <v>369</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D36" s="26">
-        <v>5.18</v>
-      </c>
-      <c r="E36" s="33" t="s">
+      <c r="D36" s="34">
+        <v>10.06</v>
+      </c>
+      <c r="E36" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="F36" s="27">
-        <v>293</v>
-      </c>
-      <c r="G36" s="24"/>
+      <c r="F36" s="35">
+        <v>195</v>
+      </c>
+      <c r="G36" s="19"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="19" t="s">
         <v>370</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D37" s="26">
-        <v>6.95</v>
-      </c>
-      <c r="E37" s="33" t="s">
+      <c r="D37" s="34">
+        <v>10.06</v>
+      </c>
+      <c r="E37" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F37" s="27">
-        <v>161</v>
-      </c>
-      <c r="G37" s="24"/>
+      <c r="F37" s="35">
+        <v>107</v>
+      </c>
+      <c r="G37" s="19"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="19" t="s">
         <v>371</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D38" s="26">
-        <v>8.57</v>
-      </c>
-      <c r="E38" s="33" t="s">
+      <c r="D38" s="34">
+        <v>13.65</v>
+      </c>
+      <c r="E38" s="23" t="s">
         <v>368</v>
       </c>
-      <c r="F38" s="27">
-        <v>137</v>
-      </c>
-      <c r="G38" s="24"/>
+      <c r="F38" s="35">
+        <v>114</v>
+      </c>
+      <c r="G38" s="19"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="19" t="s">
         <v>176</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="34">
         <v>7.5</v>
       </c>
-      <c r="E39" s="33" t="s">
+      <c r="E39" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="F39" s="27">
-        <v>102</v>
-      </c>
-      <c r="G39" s="24"/>
+      <c r="F39" s="35">
+        <v>35</v>
+      </c>
+      <c r="G39" s="19"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="19" t="s">
         <v>177</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="34">
         <v>6.98</v>
       </c>
-      <c r="E40" s="33" t="s">
+      <c r="E40" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="27">
-        <v>52</v>
-      </c>
-      <c r="G40" s="24"/>
+      <c r="F40" s="35">
+        <v>51</v>
+      </c>
+      <c r="G40" s="19"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
@@ -2484,7 +2495,7 @@
       <c r="F41" s="5">
         <v>10</v>
       </c>
-      <c r="G41" s="24"/>
+      <c r="G41" s="19"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
@@ -2496,13 +2507,13 @@
       <c r="C42" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D42" s="28">
+      <c r="D42" s="40">
         <v>10.35</v>
       </c>
-      <c r="E42" s="31" t="s">
+      <c r="E42" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="29">
+      <c r="F42" s="41">
         <v>-4</v>
       </c>
     </row>
@@ -2516,13 +2527,13 @@
       <c r="C43" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D43" s="28">
+      <c r="D43" s="40">
         <v>46.52</v>
       </c>
-      <c r="E43" s="31" t="s">
+      <c r="E43" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="F43" s="29">
+      <c r="F43" s="41">
         <v>28</v>
       </c>
     </row>
@@ -2536,14 +2547,14 @@
       <c r="C44" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D44" s="28">
+      <c r="D44" s="40">
         <v>11</v>
       </c>
-      <c r="E44" s="31" t="s">
+      <c r="E44" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F44" s="29">
-        <v>6</v>
+      <c r="F44" s="41">
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2556,13 +2567,13 @@
       <c r="C45" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D45" s="28">
+      <c r="D45" s="40">
         <v>52.19</v>
       </c>
-      <c r="E45" s="31" t="s">
+      <c r="E45" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="41">
         <v>5</v>
       </c>
     </row>
@@ -2576,14 +2587,14 @@
       <c r="C46" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D46" s="28">
+      <c r="D46" s="40">
         <v>87.74</v>
       </c>
-      <c r="E46" s="31" t="s">
+      <c r="E46" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F46" s="29">
-        <v>5</v>
+      <c r="F46" s="41">
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2594,14 +2605,14 @@
       <c r="C47" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D47" s="28">
+      <c r="D47" s="40">
         <v>15.13</v>
       </c>
-      <c r="E47" s="31" t="s">
+      <c r="E47" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="F47" s="29">
-        <v>6</v>
+      <c r="F47" s="41">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2612,14 +2623,14 @@
       <c r="C48" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D48" s="28">
+      <c r="D48" s="40">
         <v>43.63</v>
       </c>
-      <c r="E48" s="31" t="s">
+      <c r="E48" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F48" s="29">
-        <v>2</v>
+      <c r="F48" s="41">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2632,13 +2643,13 @@
       <c r="C49" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D49" s="28">
+      <c r="D49" s="40">
         <v>14.59</v>
       </c>
-      <c r="E49" s="31" t="s">
+      <c r="E49" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="F49" s="29">
+      <c r="F49" s="41">
         <v>13</v>
       </c>
     </row>
@@ -2652,61 +2663,61 @@
       <c r="C50" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D50" s="28">
+      <c r="D50" s="40">
         <v>36.869999999999997</v>
       </c>
-      <c r="E50" s="31" t="s">
+      <c r="E50" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="F50" s="29">
-        <v>3</v>
+      <c r="F50" s="41">
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="14"/>
-      <c r="B51" s="30" t="s">
+      <c r="B51" s="20" t="s">
         <v>188</v>
       </c>
       <c r="C51" s="16"/>
-      <c r="D51" s="28">
+      <c r="D51" s="40">
         <v>24.14</v>
       </c>
-      <c r="E51" s="32" t="s">
+      <c r="E51" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F51" s="29">
+      <c r="F51" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="14"/>
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="20" t="s">
         <v>189</v>
       </c>
       <c r="C52" s="16"/>
-      <c r="D52" s="28">
+      <c r="D52" s="40">
         <v>12.46</v>
       </c>
-      <c r="E52" s="32" t="s">
+      <c r="E52" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F52" s="29">
+      <c r="F52" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="14"/>
-      <c r="B53" s="30" t="s">
+      <c r="B53" s="20" t="s">
         <v>190</v>
       </c>
       <c r="C53" s="16"/>
-      <c r="D53" s="28">
+      <c r="D53" s="40">
         <v>60.84</v>
       </c>
-      <c r="E53" s="32" t="s">
+      <c r="E53" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="F53" s="29">
+      <c r="F53" s="41">
         <v>0</v>
       </c>
     </row>
@@ -2718,14 +2729,14 @@
       <c r="C54" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D54" s="28">
+      <c r="D54" s="40">
         <v>28.75</v>
       </c>
-      <c r="E54" s="31" t="s">
+      <c r="E54" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F54" s="29">
-        <v>11</v>
+      <c r="F54" s="41">
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2736,14 +2747,14 @@
       <c r="C55" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D55" s="28">
+      <c r="D55" s="40">
         <v>58.82</v>
       </c>
-      <c r="E55" s="31" t="s">
+      <c r="E55" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F55" s="29">
-        <v>8</v>
+      <c r="F55" s="41">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2754,14 +2765,14 @@
       <c r="C56" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D56" s="28">
+      <c r="D56" s="40">
         <v>23.490000000000002</v>
       </c>
-      <c r="E56" s="31" t="s">
+      <c r="E56" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="F56" s="29">
-        <v>5</v>
+      <c r="F56" s="41">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2772,61 +2783,61 @@
       <c r="C57" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D57" s="28">
+      <c r="D57" s="40">
         <v>59.9</v>
       </c>
-      <c r="E57" s="31" t="s">
+      <c r="E57" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F57" s="29">
-        <v>8</v>
+      <c r="F57" s="41">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="14"/>
-      <c r="B58" s="30" t="s">
+      <c r="B58" s="20" t="s">
         <v>195</v>
       </c>
       <c r="C58" s="16"/>
-      <c r="D58" s="28">
+      <c r="D58" s="40">
         <v>8.36</v>
       </c>
-      <c r="E58" s="32" t="s">
+      <c r="E58" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="F58" s="29">
+      <c r="F58" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="14"/>
-      <c r="B59" s="30" t="s">
+      <c r="B59" s="20" t="s">
         <v>196</v>
       </c>
       <c r="C59" s="16"/>
-      <c r="D59" s="28">
+      <c r="D59" s="40">
         <v>33.200000000000003</v>
       </c>
-      <c r="E59" s="32" t="s">
+      <c r="E59" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="F59" s="29">
+      <c r="F59" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="14"/>
-      <c r="B60" s="30" t="s">
+      <c r="B60" s="20" t="s">
         <v>197</v>
       </c>
       <c r="C60" s="16"/>
-      <c r="D60" s="28">
+      <c r="D60" s="40">
         <v>39.57</v>
       </c>
-      <c r="E60" s="32" t="s">
+      <c r="E60" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F60" s="29">
+      <c r="F60" s="41">
         <v>0</v>
       </c>
     </row>
@@ -2840,14 +2851,14 @@
       <c r="C61" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D61" s="28">
+      <c r="D61" s="40">
         <v>18.5</v>
       </c>
-      <c r="E61" s="31" t="s">
+      <c r="E61" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="F61" s="29">
-        <v>13</v>
+      <c r="F61" s="41">
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2860,14 +2871,14 @@
       <c r="C62" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D62" s="28">
+      <c r="D62" s="40">
         <v>20.990000000000002</v>
       </c>
-      <c r="E62" s="31" t="s">
+      <c r="E62" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="F62" s="29">
-        <v>11</v>
+      <c r="F62" s="41">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2880,14 +2891,14 @@
       <c r="C63" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D63" s="28">
+      <c r="D63" s="40">
         <v>48.1</v>
       </c>
-      <c r="E63" s="31" t="s">
+      <c r="E63" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F63" s="29">
-        <v>3</v>
+      <c r="F63" s="41">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2900,13 +2911,13 @@
       <c r="C64" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D64" s="28">
+      <c r="D64" s="40">
         <v>51.81</v>
       </c>
-      <c r="E64" s="31" t="s">
+      <c r="E64" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="F64" s="29">
+      <c r="F64" s="41">
         <v>7</v>
       </c>
     </row>
@@ -2920,13 +2931,13 @@
       <c r="C65" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D65" s="39">
-        <v>65.8</v>
+      <c r="D65" s="42">
+        <v>69.08</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F65" s="40">
+      <c r="F65" s="43">
         <v>1</v>
       </c>
     </row>
@@ -2940,28 +2951,28 @@
       <c r="C66" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D66" s="39">
-        <v>129.94999999999999</v>
+      <c r="D66" s="42">
+        <v>136.44999999999999</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F66" s="40">
-        <v>2</v>
+      <c r="F66" s="43">
+        <v>-1</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
-      <c r="B67" s="30" t="s">
+      <c r="B67" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="D67" s="39">
+      <c r="D67" s="42">
         <v>255.92000000000002</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F67" s="40">
+      <c r="F67" s="43">
         <v>0</v>
       </c>
     </row>
@@ -2975,14 +2986,14 @@
       <c r="C68" s="2">
         <v>100</v>
       </c>
-      <c r="D68" s="39">
+      <c r="D68" s="42">
         <v>11.8</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F68" s="40">
-        <v>0</v>
+      <c r="F68" s="43">
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2995,13 +3006,13 @@
       <c r="C69" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D69" s="39">
+      <c r="D69" s="42">
         <v>13.36</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F69" s="40">
+      <c r="F69" s="43">
         <v>5</v>
       </c>
     </row>
@@ -3015,14 +3026,14 @@
       <c r="C70" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D70" s="39">
-        <v>13.36</v>
+      <c r="D70" s="42">
+        <v>14.040000000000001</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F70" s="40">
-        <v>2</v>
+      <c r="F70" s="43">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -3035,14 +3046,14 @@
       <c r="C71" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D71" s="39">
-        <v>13.36</v>
+      <c r="D71" s="42">
+        <v>14.040000000000001</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="F71" s="40">
-        <v>2</v>
+      <c r="F71" s="43">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3055,14 +3066,14 @@
       <c r="C72" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D72" s="39">
+      <c r="D72" s="42">
         <v>14.14</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F72" s="40">
-        <v>3</v>
+      <c r="F72" s="43">
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -3075,14 +3086,14 @@
       <c r="C73" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D73" s="39">
+      <c r="D73" s="42">
         <v>12.780000000000001</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F73" s="40">
-        <v>1</v>
+      <c r="F73" s="43">
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3095,13 +3106,13 @@
       <c r="C74" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D74" s="39">
-        <v>13.200000000000001</v>
+      <c r="D74" s="42">
+        <v>14.07</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="F74" s="40">
+      <c r="F74" s="43">
         <v>3</v>
       </c>
     </row>
@@ -3115,32 +3126,32 @@
       <c r="C75" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D75" s="39">
+      <c r="D75" s="42">
         <v>14.35</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F75" s="40">
-        <v>5</v>
+      <c r="F75" s="43">
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="14"/>
-      <c r="B76" s="30" t="s">
+      <c r="B76" s="20" t="s">
         <v>212</v>
       </c>
       <c r="C76" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D76" s="39">
+      <c r="D76" s="42">
         <v>31.02</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F76" s="40">
-        <v>-2</v>
+      <c r="F76" s="43">
+        <v>-5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3153,13 +3164,13 @@
       <c r="C77" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D77" s="39">
-        <v>24.88</v>
+      <c r="D77" s="42">
+        <v>26.12</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F77" s="40">
+      <c r="F77" s="43">
         <v>4</v>
       </c>
     </row>
@@ -3173,14 +3184,14 @@
       <c r="C78" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D78" s="39">
+      <c r="D78" s="42">
         <v>28.64</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F78" s="40">
-        <v>8</v>
+      <c r="F78" s="43">
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3193,14 +3204,14 @@
       <c r="C79" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D79" s="39">
-        <v>28.22</v>
+      <c r="D79" s="42">
+        <v>30.060000000000002</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F79" s="40">
-        <v>2</v>
+      <c r="F79" s="43">
+        <v>-1</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -3213,14 +3224,14 @@
       <c r="C80" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D80" s="39">
-        <v>28.650000000000002</v>
+      <c r="D80" s="42">
+        <v>30.07</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F80" s="40">
-        <v>6</v>
+      <c r="F80" s="43">
+        <v>-1</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3233,14 +3244,14 @@
       <c r="C81" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D81" s="39">
-        <v>20.61</v>
+      <c r="D81" s="42">
+        <v>21.650000000000002</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F81" s="40">
-        <v>7</v>
+      <c r="F81" s="43">
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3253,14 +3264,14 @@
       <c r="C82" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D82" s="39">
-        <v>28.68</v>
+      <c r="D82" s="42">
+        <v>30.09</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F82" s="40">
-        <v>6</v>
+      <c r="F82" s="43">
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3273,13 +3284,13 @@
       <c r="C83" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D83" s="39">
+      <c r="D83" s="42">
         <v>25.92</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F83" s="40">
+      <c r="F83" s="43">
         <v>5</v>
       </c>
     </row>
@@ -3293,13 +3304,13 @@
       <c r="C84" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D84" s="39">
-        <v>27.87</v>
+      <c r="D84" s="42">
+        <v>29.25</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="F84" s="40">
+      <c r="F84" s="43">
         <v>4</v>
       </c>
     </row>
@@ -3313,13 +3324,13 @@
       <c r="C85" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D85" s="39">
-        <v>28.64</v>
+      <c r="D85" s="42">
+        <v>30.060000000000002</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F85" s="40">
+      <c r="F85" s="43">
         <v>6</v>
       </c>
     </row>
@@ -3333,13 +3344,13 @@
       <c r="C86" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D86" s="39">
+      <c r="D86" s="42">
         <v>19.7</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F86" s="40">
+      <c r="F86" s="43">
         <v>0</v>
       </c>
     </row>
@@ -3347,17 +3358,17 @@
       <c r="A87" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B87" s="30" t="s">
+      <c r="B87" s="20" t="s">
         <v>223</v>
       </c>
       <c r="C87" s="16"/>
-      <c r="D87" s="39">
+      <c r="D87" s="42">
         <v>79.86</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="F87" s="40">
+      <c r="F87" s="43">
         <v>5</v>
       </c>
     </row>
@@ -3371,14 +3382,14 @@
       <c r="C88" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D88" s="39">
+      <c r="D88" s="42">
         <v>111.09</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F88" s="40">
-        <v>1</v>
+      <c r="F88" s="43">
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -3391,13 +3402,13 @@
       <c r="C89" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D89" s="39">
+      <c r="D89" s="42">
         <v>79.92</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F89" s="40">
+      <c r="F89" s="43">
         <v>2</v>
       </c>
     </row>
@@ -3411,13 +3422,13 @@
       <c r="C90" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D90" s="39">
+      <c r="D90" s="42">
         <v>20.7</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F90" s="40">
+      <c r="F90" s="43">
         <v>6</v>
       </c>
     </row>
@@ -3431,14 +3442,14 @@
       <c r="C91" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D91" s="39">
-        <v>56</v>
+      <c r="D91" s="42">
+        <v>58.79</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="F91" s="40">
-        <v>1</v>
+      <c r="F91" s="43">
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3451,14 +3462,14 @@
       <c r="C92" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D92" s="39">
-        <v>112</v>
+      <c r="D92" s="42">
+        <v>117.60000000000001</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F92" s="40">
-        <v>2</v>
+      <c r="F92" s="43">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3471,14 +3482,14 @@
       <c r="C93" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D93" s="39">
-        <v>65.12</v>
+      <c r="D93" s="42">
+        <v>62.160000000000004</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="40">
-        <v>4</v>
+      <c r="F93" s="43">
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3491,14 +3502,14 @@
       <c r="C94" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D94" s="39">
-        <v>12.68</v>
+      <c r="D94" s="42">
+        <v>13.32</v>
       </c>
       <c r="E94" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F94" s="40">
-        <v>3</v>
+      <c r="F94" s="43">
+        <v>-1</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3511,13 +3522,13 @@
       <c r="C95" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D95" s="39">
+      <c r="D95" s="42">
         <v>12.91</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F95" s="40">
+      <c r="F95" s="43">
         <v>7</v>
       </c>
     </row>
@@ -3531,14 +3542,14 @@
       <c r="C96" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D96" s="39">
+      <c r="D96" s="42">
         <v>27.330000000000002</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F96" s="40">
-        <v>161</v>
+      <c r="F96" s="43">
+        <v>75</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -3551,13 +3562,13 @@
       <c r="C97" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D97" s="39">
+      <c r="D97" s="42">
         <v>33.5</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F97" s="40">
+      <c r="F97" s="43">
         <v>4</v>
       </c>
     </row>
@@ -3571,14 +3582,14 @@
       <c r="C98" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D98" s="39">
-        <v>38.880000000000003</v>
+      <c r="D98" s="42">
+        <v>40.840000000000003</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F98" s="40">
-        <v>2</v>
+      <c r="F98" s="43">
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -3591,13 +3602,13 @@
       <c r="C99" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D99" s="39">
-        <v>8.66</v>
+      <c r="D99" s="42">
+        <v>9.43</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F99" s="40">
+      <c r="F99" s="43">
         <v>2</v>
       </c>
     </row>
@@ -3611,28 +3622,28 @@
       <c r="C100" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D100" s="39">
+      <c r="D100" s="42">
         <v>69.650000000000006</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F100" s="40">
+      <c r="F100" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="14"/>
-      <c r="B101" s="30" t="s">
+      <c r="B101" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="D101" s="39">
+      <c r="D101" s="42">
         <v>24.650000000000002</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F101" s="40">
+      <c r="F101" s="43">
         <v>0</v>
       </c>
     </row>
@@ -3646,28 +3657,28 @@
       <c r="C102" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D102" s="39">
-        <v>47.19</v>
+      <c r="D102" s="42">
+        <v>56.11</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F102" s="40">
-        <v>2</v>
+      <c r="F102" s="43">
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="14"/>
-      <c r="B103" s="30" t="s">
+      <c r="B103" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="D103" s="39">
+      <c r="D103" s="42">
         <v>29.080000000000002</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="F103" s="40">
+      <c r="F103" s="43">
         <v>0</v>
       </c>
     </row>
@@ -3681,14 +3692,14 @@
       <c r="C104" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D104" s="39">
+      <c r="D104" s="42">
         <v>32.69</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="F104" s="40">
-        <v>31</v>
+      <c r="F104" s="43">
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -3699,13 +3710,13 @@
       <c r="C105" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D105" s="39">
+      <c r="D105" s="42">
         <v>24.26</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F105" s="40">
+      <c r="F105" s="43">
         <v>6</v>
       </c>
     </row>
@@ -3717,13 +3728,13 @@
       <c r="C106" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D106" s="39">
+      <c r="D106" s="42">
         <v>23.1</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F106" s="40">
+      <c r="F106" s="43">
         <v>5</v>
       </c>
     </row>
@@ -3735,29 +3746,29 @@
       <c r="C107" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D107" s="39">
+      <c r="D107" s="42">
         <v>7.8</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="F107" s="40">
-        <v>2</v>
+      <c r="F107" s="43">
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="14"/>
-      <c r="B108" s="30" t="s">
+      <c r="B108" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="D108" s="39">
+      <c r="D108" s="42">
         <v>7.66</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F108" s="40">
-        <v>16</v>
+      <c r="F108" s="43">
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -3765,13 +3776,13 @@
       <c r="B109" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="D109" s="39">
+      <c r="D109" s="42">
         <v>17.16</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F109" s="40">
+      <c r="F109" s="43">
         <v>4</v>
       </c>
     </row>
@@ -3783,14 +3794,14 @@
       <c r="C110" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D110" s="39">
+      <c r="D110" s="42">
         <v>16.830000000000002</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F110" s="40">
-        <v>11</v>
+      <c r="F110" s="43">
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -3801,14 +3812,14 @@
       <c r="C111" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D111" s="39">
+      <c r="D111" s="42">
         <v>8.6</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F111" s="40">
-        <v>22</v>
+      <c r="F111" s="43">
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -3819,14 +3830,14 @@
       <c r="C112" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D112" s="39">
+      <c r="D112" s="42">
         <v>32.130000000000003</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F112" s="40">
-        <v>35</v>
+      <c r="F112" s="43">
+        <v>46</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -3837,14 +3848,14 @@
       <c r="C113" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D113" s="39">
+      <c r="D113" s="42">
         <v>33.090000000000003</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F113" s="40">
-        <v>11</v>
+      <c r="F113" s="43">
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3855,13 +3866,13 @@
       <c r="C114" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D114" s="39">
+      <c r="D114" s="42">
         <v>8.86</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F114" s="40">
+      <c r="F114" s="43">
         <v>-1</v>
       </c>
     </row>
@@ -3875,14 +3886,14 @@
       <c r="C115" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D115" s="39">
+      <c r="D115" s="42">
         <v>19.41</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F115" s="40">
-        <v>4</v>
+      <c r="F115" s="43">
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -3895,13 +3906,13 @@
       <c r="C116" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D116" s="39">
+      <c r="D116" s="42">
         <v>65.33</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F116" s="40">
+      <c r="F116" s="43">
         <v>3</v>
       </c>
     </row>
@@ -3913,14 +3924,14 @@
       <c r="C117" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D117" s="39">
+      <c r="D117" s="42">
         <v>11.82</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F117" s="40">
-        <v>10</v>
+      <c r="F117" s="43">
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -3933,14 +3944,14 @@
       <c r="C118" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D118" s="39">
+      <c r="D118" s="42">
         <v>35.56</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F118" s="40">
-        <v>5</v>
+      <c r="F118" s="43">
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -3953,13 +3964,13 @@
       <c r="C119" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D119" s="39">
+      <c r="D119" s="42">
         <v>89.14</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F119" s="40">
+      <c r="F119" s="43">
         <v>4</v>
       </c>
     </row>
@@ -3971,13 +3982,13 @@
       <c r="C120" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D120" s="39">
+      <c r="D120" s="42">
         <v>24.32</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F120" s="40">
+      <c r="F120" s="43">
         <v>4</v>
       </c>
     </row>
@@ -3989,13 +4000,13 @@
       <c r="C121" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D121" s="39">
+      <c r="D121" s="42">
         <v>31.240000000000002</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F121" s="40">
+      <c r="F121" s="43">
         <v>4</v>
       </c>
     </row>
@@ -4007,13 +4018,13 @@
       <c r="C122" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D122" s="39">
+      <c r="D122" s="42">
         <v>28.82</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F122" s="40">
+      <c r="F122" s="43">
         <v>4</v>
       </c>
     </row>
@@ -4025,13 +4036,13 @@
       <c r="C123" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D123" s="39">
+      <c r="D123" s="42">
         <v>72.710000000000008</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F123" s="40">
+      <c r="F123" s="43">
         <v>3</v>
       </c>
     </row>
@@ -4043,13 +4054,13 @@
       <c r="C124" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D124" s="39">
+      <c r="D124" s="42">
         <v>9.84</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F124" s="40">
+      <c r="F124" s="43">
         <v>12</v>
       </c>
     </row>
@@ -4061,13 +4072,13 @@
       <c r="C125" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D125" s="39">
+      <c r="D125" s="42">
         <v>23.8</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F125" s="40">
+      <c r="F125" s="43">
         <v>2</v>
       </c>
     </row>
@@ -4079,13 +4090,13 @@
       <c r="C126" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D126" s="39">
+      <c r="D126" s="42">
         <v>35.68</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F126" s="40">
+      <c r="F126" s="43">
         <v>0</v>
       </c>
     </row>
@@ -4097,14 +4108,14 @@
       <c r="C127" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D127" s="39">
+      <c r="D127" s="42">
         <v>18.22</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F127" s="40">
-        <v>8</v>
+      <c r="F127" s="43">
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
@@ -4115,14 +4126,14 @@
       <c r="C128" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D128" s="39">
+      <c r="D128" s="42">
         <v>18.150000000000002</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F128" s="40">
-        <v>3</v>
+      <c r="F128" s="43">
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -4133,14 +4144,14 @@
       <c r="C129" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D129" s="39">
+      <c r="D129" s="42">
         <v>15.63</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F129" s="40">
-        <v>18</v>
+      <c r="F129" s="43">
+        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -4151,13 +4162,13 @@
       <c r="C130" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D130" s="39">
+      <c r="D130" s="42">
         <v>29.5</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F130" s="40">
+      <c r="F130" s="43">
         <v>3</v>
       </c>
     </row>
@@ -4169,14 +4180,14 @@
       <c r="C131" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D131" s="39">
+      <c r="D131" s="42">
         <v>49.51</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F131" s="40">
-        <v>10</v>
+      <c r="F131" s="43">
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -4187,43 +4198,43 @@
       <c r="C132" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D132" s="39">
+      <c r="D132" s="42">
         <v>64</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F132" s="40">
+      <c r="F132" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="14"/>
-      <c r="B133" s="30" t="s">
+      <c r="B133" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="D133" s="39">
+      <c r="D133" s="42">
         <v>18.37</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F133" s="40">
+      <c r="F133" s="43">
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="14"/>
-      <c r="B134" s="30" t="s">
+      <c r="B134" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="D134" s="39">
+      <c r="D134" s="42">
         <v>39.57</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F134" s="40">
+      <c r="F134" s="43">
         <v>-1</v>
       </c>
     </row>
@@ -4235,28 +4246,28 @@
       <c r="C135" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D135" s="39">
+      <c r="D135" s="42">
         <v>44.78</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F135" s="40">
-        <v>1</v>
+      <c r="F135" s="43">
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="14"/>
-      <c r="B136" s="30" t="s">
+      <c r="B136" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="D136" s="39">
+      <c r="D136" s="42">
         <v>44.61</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F136" s="40">
+      <c r="F136" s="43">
         <v>3</v>
       </c>
     </row>
@@ -4270,13 +4281,13 @@
       <c r="C137" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D137" s="39">
+      <c r="D137" s="42">
         <v>25.22</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F137" s="40">
+      <c r="F137" s="43">
         <v>1</v>
       </c>
     </row>
@@ -4290,13 +4301,13 @@
       <c r="C138" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D138" s="39">
+      <c r="D138" s="42">
         <v>52.01</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F138" s="40">
+      <c r="F138" s="43">
         <v>2</v>
       </c>
     </row>
@@ -4310,21 +4321,21 @@
       <c r="C139" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D139" s="39">
+      <c r="D139" s="42">
         <v>24.32</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F139" s="40">
-        <v>7</v>
+      <c r="F139" s="43">
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B140" s="38" t="s">
+      <c r="B140" s="28" t="s">
         <v>302</v>
       </c>
       <c r="C140" s="2" t="s">
@@ -4333,7 +4344,7 @@
       <c r="D140" s="5">
         <v>23.4</v>
       </c>
-      <c r="E140" s="36" t="s">
+      <c r="E140" s="26" t="s">
         <v>363</v>
       </c>
       <c r="F140" s="5">
@@ -4344,7 +4355,7 @@
       <c r="A141" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B141" s="38" t="s">
+      <c r="B141" s="28" t="s">
         <v>303</v>
       </c>
       <c r="C141" s="2" t="s">
@@ -4353,7 +4364,7 @@
       <c r="D141" s="5">
         <v>14.37</v>
       </c>
-      <c r="E141" s="36" t="s">
+      <c r="E141" s="26" t="s">
         <v>301</v>
       </c>
       <c r="F141" s="5">
@@ -4364,7 +4375,7 @@
       <c r="A142" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="B142" s="38" t="s">
+      <c r="B142" s="28" t="s">
         <v>348</v>
       </c>
       <c r="C142" s="2" t="s">
@@ -4377,27 +4388,27 @@
         <v>343</v>
       </c>
       <c r="F142" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="B143" s="38" t="s">
+      <c r="B143" s="28" t="s">
         <v>344</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>284</v>
       </c>
       <c r="D143" s="5">
-        <v>29.35</v>
-      </c>
-      <c r="E143" s="37" t="s">
+        <v>30.09</v>
+      </c>
+      <c r="E143" s="27" t="s">
         <v>345</v>
       </c>
       <c r="F143" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -4417,7 +4428,7 @@
         <v>346</v>
       </c>
       <c r="F144" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
